--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VOO" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VXUS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BND" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BIL" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VSS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TLT" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VWO" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LQD" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IEF" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SHY" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QQQ" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="@總表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="VOO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="VXUS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BND" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="BIL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="VSS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TLT" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VWO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="LQD" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IEF" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SHY" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="QQQ" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="外部資料_1" localSheetId="1" hidden="1">VOO!#REF!</definedName>
@@ -3080,20 +3080,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>96.06999999999999</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -3399,20 +3399,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>83.12</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>83.12</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>83.12</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>83.12</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -3717,20 +3717,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>475.47</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>475.47</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>475.47</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>475.47</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -4036,20 +4036,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>509.74</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>509.74</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>509.74</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>509.74</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -4355,20 +4355,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>63.86</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>63.86</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>63.86</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>63.86</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -4675,20 +4675,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>73.5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>73.5</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>73.5</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>73.5</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -4993,20 +4993,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>91.72</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>91.72</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>91.72</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>91.72</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -5312,20 +5312,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>120.42</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>120.42</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>120.42</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>120.42</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -5629,20 +5629,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>89.47</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>89.47</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>89.47</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>89.47</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -5948,20 +5948,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>45.25</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>45.25</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>45.25</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>45.25</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>
@@ -6266,20 +6266,20 @@
       <c r="A14" s="37" t="n">
         <v>45748</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>107.98</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>107.98</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="0" t="n">
         <v>107.98</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>107.98</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
     </row>
     <row r="15" ht="19.2" customHeight="1" s="28"/>
     <row r="16" ht="19.2" customHeight="1" s="28"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>95.93000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>95.93000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>95.93000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>95.93000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>95.44</v>
+        <v>94.98</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>95.44</v>
+        <v>94.98</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>95.44</v>
+        <v>94.98</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>95.44</v>
+        <v>94.98</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>95.44</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>95.94</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>95.94</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>95.94</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>95.94</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>96.16</v>
+        <v>95.94</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>96.16</v>
+        <v>95.94</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>96.16</v>
+        <v>95.94</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>96.16</v>
+        <v>95.94</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>97.5</v>
+        <v>96.16</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>97.5</v>
+        <v>96.16</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>97.5</v>
+        <v>96.16</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>97.5</v>
+        <v>96.16</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>96.45999999999999</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>95.77</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>95.77</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>95.77</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>95.77</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>96.06999999999999</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>96.06999999999999</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>96.06999999999999</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>96.06999999999999</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.64</v>
+        <v>82.25</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.64</v>
+        <v>82.25</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.64</v>
+        <v>82.25</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.64</v>
+        <v>82.25</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>83.08</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>83.08</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>83.08</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>83.08</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>82.98</v>
+        <v>83.08</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>82.98</v>
+        <v>83.08</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>82.98</v>
+        <v>83.08</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>82.98</v>
+        <v>83.08</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>82.98</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>82.98</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>82.98</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>82.98</v>
+        <v>82.95999999999999</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>82.52</v>
+        <v>82.98</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>82.52</v>
+        <v>82.98</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>82.52</v>
+        <v>82.98</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>82.52</v>
+        <v>82.98</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>82.86</v>
+        <v>82.52</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>82.86</v>
+        <v>82.52</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>82.86</v>
+        <v>82.52</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>82.86</v>
+        <v>82.52</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>82.86</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>83.12</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>83.12</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>83.12</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>83.12</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>648.85</v>
+        <v>674.15</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>648.85</v>
+        <v>674.15</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>648.85</v>
+        <v>674.15</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>648.85</v>
+        <v>674.15</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>667.74</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>667.74</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>667.74</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>667.74</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>607.29</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>607.29</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>607.29</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>607.29</v>
+        <v>577.1799999999999</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>621.87</v>
+        <v>607.29</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>621.87</v>
+        <v>607.29</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>621.87</v>
+        <v>607.29</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>621.87</v>
+        <v>607.29</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>621.87</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>621.87</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>621.87</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>621.87</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>619.25</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>619.25</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>619.25</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>619.25</v>
+        <v>614.3099999999999</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>619.25</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>619.25</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>619.25</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>619.25</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>600.37</v>
+        <v>629.0700000000001</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>600.37</v>
+        <v>629.0700000000001</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>600.37</v>
+        <v>629.0700000000001</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>600.37</v>
+        <v>629.0700000000001</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>570.4</v>
+        <v>600.37</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>570.4</v>
+        <v>600.37</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>570.4</v>
+        <v>600.37</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>570.4</v>
+        <v>600.37</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>565.01</v>
+        <v>570.4</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>565.01</v>
+        <v>570.4</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>565.01</v>
+        <v>570.4</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>565.01</v>
+        <v>570.4</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>551.64</v>
+        <v>565.01</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>551.64</v>
+        <v>565.01</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>551.64</v>
+        <v>565.01</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>551.64</v>
+        <v>565.01</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>519.11</v>
+        <v>551.64</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>519.11</v>
+        <v>551.64</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>519.11</v>
+        <v>551.64</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>519.11</v>
+        <v>551.64</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>475.47</v>
+        <v>519.11</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>475.47</v>
+        <v>519.11</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>475.47</v>
+        <v>519.11</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>475.47</v>
+        <v>519.11</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>652.78</v>
+        <v>662.52</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>652.78</v>
+        <v>662.52</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>652.78</v>
+        <v>662.52</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>652.78</v>
+        <v>662.52</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>597.55</v>
+        <v>660.58</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>597.55</v>
+        <v>660.58</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>597.55</v>
+        <v>660.58</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>597.55</v>
+        <v>660.58</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>631.04</v>
+        <v>597.55</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>631.04</v>
+        <v>597.55</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>631.04</v>
+        <v>597.55</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>631.04</v>
+        <v>597.55</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>636.22</v>
+        <v>631.04</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>636.22</v>
+        <v>631.04</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>636.22</v>
+        <v>631.04</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>636.22</v>
+        <v>631.04</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>627.13</v>
+        <v>636.22</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>627.13</v>
+        <v>636.22</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>627.13</v>
+        <v>636.22</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>627.13</v>
+        <v>636.22</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>628.41</v>
+        <v>627.13</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>628.41</v>
+        <v>627.13</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>628.41</v>
+        <v>627.13</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>628.41</v>
+        <v>627.13</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>627.04</v>
+        <v>628.41</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>627.04</v>
+        <v>628.41</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>627.04</v>
+        <v>628.41</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>627.04</v>
+        <v>628.41</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>612.38</v>
+        <v>627.04</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>612.38</v>
+        <v>627.04</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>612.38</v>
+        <v>627.04</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>612.38</v>
+        <v>627.04</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>593.08</v>
+        <v>612.38</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>593.08</v>
+        <v>612.38</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>593.08</v>
+        <v>612.38</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>593.08</v>
+        <v>612.38</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>581.02</v>
+        <v>593.08</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>581.02</v>
+        <v>593.08</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>581.02</v>
+        <v>593.08</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>581.02</v>
+        <v>593.08</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>568.03</v>
+        <v>581.02</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>568.03</v>
+        <v>581.02</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>568.03</v>
+        <v>581.02</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>568.03</v>
+        <v>581.02</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>541.76</v>
+        <v>568.03</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>541.76</v>
+        <v>568.03</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>541.76</v>
+        <v>568.03</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>541.76</v>
+        <v>568.03</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>509.74</v>
+        <v>541.76</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>509.74</v>
+        <v>541.76</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>509.74</v>
+        <v>541.76</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>509.74</v>
+        <v>541.76</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>83.75</v>
+        <v>82.97</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>83.75</v>
+        <v>82.97</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>83.75</v>
+        <v>82.97</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>83.75</v>
+        <v>82.97</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>77.11</v>
+        <v>83.06</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>77.11</v>
+        <v>83.06</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>77.11</v>
+        <v>83.06</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>77.11</v>
+        <v>83.06</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>83.81</v>
+        <v>77.11</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>83.81</v>
+        <v>77.11</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>83.81</v>
+        <v>77.11</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>83.81</v>
+        <v>77.11</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>79.66</v>
+        <v>83.81</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>79.66</v>
+        <v>83.81</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>79.66</v>
+        <v>83.81</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>79.66</v>
+        <v>83.81</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>75.44</v>
+        <v>79.66</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>75.44</v>
+        <v>79.66</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>75.44</v>
+        <v>79.66</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>75.44</v>
+        <v>79.66</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>74.94</v>
+        <v>75.44</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>74.94</v>
+        <v>75.44</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>74.94</v>
+        <v>75.44</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>74.94</v>
+        <v>75.44</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>74.63</v>
+        <v>74.94</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>74.63</v>
+        <v>74.94</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>74.63</v>
+        <v>74.94</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>74.63</v>
+        <v>74.94</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>74.63</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>71.37</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>71.37</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>71.37</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>71.37</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>68.47</v>
+        <v>71.37</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>68.47</v>
+        <v>71.37</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>68.47</v>
+        <v>71.37</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>68.47</v>
+        <v>71.37</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>69.09</v>
+        <v>68.47</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>69.09</v>
+        <v>68.47</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>69.09</v>
+        <v>68.47</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>69.09</v>
+        <v>68.47</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>66.94</v>
+        <v>69.09</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>66.94</v>
+        <v>69.09</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>66.94</v>
+        <v>69.09</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>66.94</v>
+        <v>69.09</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>63.86</v>
+        <v>66.94</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>63.86</v>
+        <v>66.94</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>63.86</v>
+        <v>66.94</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>63.86</v>
+        <v>66.94</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>74.06</v>
+        <v>73.36</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>74.06</v>
+        <v>73.36</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>74.06</v>
+        <v>73.36</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>74.06</v>
+        <v>73.36</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.64</v>
+        <v>73.5</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.64</v>
+        <v>73.5</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.64</v>
+        <v>73.5</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.64</v>
+        <v>73.5</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>75.17</v>
+        <v>73.64</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>75.17</v>
+        <v>73.64</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>75.17</v>
+        <v>73.64</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>75.17</v>
+        <v>73.64</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>74.23</v>
+        <v>75.17</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>74.23</v>
+        <v>75.17</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>74.23</v>
+        <v>75.17</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>74.23</v>
+        <v>75.17</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>74.78</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>74.78</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>74.78</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>74.78</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>74.58</v>
+        <v>74.78</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>74.58</v>
+        <v>74.78</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>74.58</v>
+        <v>74.78</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>74.58</v>
+        <v>74.78</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>74.37</v>
+        <v>74.58</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>74.37</v>
+        <v>74.58</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>74.37</v>
+        <v>74.58</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>74.37</v>
+        <v>74.58</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>73.8</v>
+        <v>74.37</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>73.8</v>
+        <v>74.37</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>73.8</v>
+        <v>74.37</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>73.8</v>
+        <v>74.37</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>73.63</v>
+        <v>73.2</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>73.63</v>
+        <v>73.2</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>73.63</v>
+        <v>73.2</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>73.63</v>
+        <v>73.2</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>72.77</v>
+        <v>73.63</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>72.77</v>
+        <v>73.63</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>72.77</v>
+        <v>73.63</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>72.77</v>
+        <v>73.63</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>73.5</v>
+        <v>72.77</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>73.5</v>
+        <v>72.77</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>73.5</v>
+        <v>72.77</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>73.5</v>
+        <v>72.77</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,26 +4763,26 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>91.64</v>
@@ -4801,209 +4801,209 @@
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>91.62</v>
+        <v>91.64</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>91.62</v>
+        <v>91.64</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>91.62</v>
+        <v>91.64</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>91.62</v>
+        <v>91.64</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>91.62</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>91.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>91.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>91.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>91.38</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>91.72</v>
+        <v>91.38</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>91.72</v>
+        <v>91.38</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>91.72</v>
+        <v>91.38</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>91.72</v>
+        <v>91.38</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>91.72</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>91.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>91.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>91.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>91.75</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>91.77</v>
+        <v>91.75</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>91.77</v>
+        <v>91.75</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>91.77</v>
+        <v>91.75</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>91.77</v>
+        <v>91.75</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>91.75</v>
+        <v>91.77</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>91.75</v>
+        <v>91.77</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>91.75</v>
+        <v>91.77</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>91.75</v>
+        <v>91.77</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>91.73</v>
+        <v>91.75</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>91.73</v>
+        <v>91.75</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>91.73</v>
+        <v>91.75</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>91.73</v>
+        <v>91.75</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.72</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.72</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.72</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.72</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>160.24</v>
+        <v>157.72</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>160.24</v>
+        <v>157.72</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>160.24</v>
+        <v>157.72</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>160.24</v>
+        <v>157.72</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>145.79</v>
+        <v>158.09</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>145.79</v>
+        <v>158.09</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>145.79</v>
+        <v>158.09</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>145.79</v>
+        <v>158.09</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>160.05</v>
+        <v>145.79</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>160.05</v>
+        <v>145.79</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>160.05</v>
+        <v>145.79</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>160.05</v>
+        <v>145.79</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.05</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.05</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.05</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.05</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>143.33</v>
+        <v>152.5</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>143.33</v>
+        <v>152.5</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>143.33</v>
+        <v>152.5</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>143.33</v>
+        <v>152.5</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>143.76</v>
+        <v>143.33</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>143.76</v>
+        <v>143.33</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>143.76</v>
+        <v>143.33</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>143.76</v>
+        <v>143.33</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>142.36</v>
+        <v>143.76</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>142.36</v>
+        <v>143.76</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>142.36</v>
+        <v>143.76</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>142.36</v>
+        <v>143.76</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>142.55</v>
+        <v>142.36</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>142.55</v>
+        <v>142.36</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>142.55</v>
+        <v>142.36</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>142.55</v>
+        <v>142.36</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>140.27</v>
+        <v>142.55</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>140.27</v>
+        <v>142.55</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>140.27</v>
+        <v>142.55</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>140.27</v>
+        <v>142.55</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>133.68</v>
+        <v>140.27</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>133.68</v>
+        <v>140.27</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>133.68</v>
+        <v>140.27</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>133.68</v>
+        <v>140.27</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>134.39</v>
+        <v>133.68</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>134.39</v>
+        <v>133.68</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>134.39</v>
+        <v>133.68</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>134.39</v>
+        <v>133.68</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>127.69</v>
+        <v>134.39</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>127.69</v>
+        <v>134.39</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>127.69</v>
+        <v>134.39</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>127.69</v>
+        <v>134.39</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>120.42</v>
+        <v>127.69</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>120.42</v>
+        <v>127.69</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>120.42</v>
+        <v>127.69</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>120.42</v>
+        <v>127.69</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>87.06999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>87.06999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>87.06999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>87.06999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>86.69</v>
+        <v>85.62</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>86.69</v>
+        <v>85.62</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>86.69</v>
+        <v>85.62</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>86.69</v>
+        <v>85.62</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>86.69</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>87.13</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>87.13</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>87.13</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>87.13</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>87.16</v>
+        <v>87.13</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>87.16</v>
+        <v>87.13</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>87.16</v>
+        <v>87.13</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>87.16</v>
+        <v>87.13</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.16</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.37</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.37</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.37</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.37</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>89.37</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>86.92</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>86.92</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>86.92</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>86.92</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.25</v>
+        <v>86.92</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.25</v>
+        <v>86.92</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.25</v>
+        <v>86.92</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.25</v>
+        <v>86.92</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>86.28</v>
+        <v>88.25</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>86.28</v>
+        <v>88.25</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>86.28</v>
+        <v>88.25</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>86.28</v>
+        <v>88.25</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>89.47</v>
+        <v>86.28</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>89.47</v>
+        <v>86.28</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>89.47</v>
+        <v>86.28</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>89.47</v>
+        <v>86.28</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>59.18</v>
+        <v>58.99</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>59.18</v>
+        <v>58.99</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>59.18</v>
+        <v>58.99</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>59.18</v>
+        <v>58.99</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>54.05</v>
+        <v>58.93</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>54.05</v>
+        <v>58.93</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>54.05</v>
+        <v>58.93</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>54.05</v>
+        <v>58.93</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>58.1</v>
+        <v>54.05</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>58.1</v>
+        <v>54.05</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>58.1</v>
+        <v>54.05</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>58.1</v>
+        <v>54.05</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>56.47</v>
+        <v>58.1</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>56.47</v>
+        <v>58.1</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>56.47</v>
+        <v>58.1</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>56.47</v>
+        <v>58.1</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>53.76</v>
+        <v>56.47</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>53.76</v>
+        <v>56.47</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>53.76</v>
+        <v>56.47</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>53.76</v>
+        <v>56.47</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>54.3</v>
+        <v>53.76</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>54.3</v>
+        <v>53.76</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>54.3</v>
+        <v>53.76</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>54.3</v>
+        <v>53.76</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>54.97</v>
+        <v>54.3</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>54.97</v>
+        <v>54.3</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>54.97</v>
+        <v>54.3</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>54.97</v>
+        <v>54.3</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>54.18</v>
+        <v>54.97</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>54.18</v>
+        <v>54.97</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>54.18</v>
+        <v>54.97</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>54.18</v>
+        <v>54.97</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>51.53</v>
+        <v>54.18</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>51.53</v>
+        <v>54.18</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>51.53</v>
+        <v>54.18</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>51.53</v>
+        <v>54.18</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>49.8</v>
+        <v>51.53</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>49.8</v>
+        <v>51.53</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>49.8</v>
+        <v>51.53</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>49.8</v>
+        <v>51.53</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>49.46</v>
+        <v>49.8</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>49.46</v>
+        <v>49.8</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>49.46</v>
+        <v>49.8</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>49.46</v>
+        <v>49.8</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>47</v>
+        <v>49.46</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>47</v>
+        <v>49.46</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>47</v>
+        <v>49.46</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>47</v>
+        <v>49.46</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>45.25</v>
+        <v>47</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>45.25</v>
+        <v>47</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>45.25</v>
+        <v>47</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>45.25</v>
+        <v>47</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>110.04</v>
+        <v>108.6</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>110.04</v>
+        <v>108.6</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>110.04</v>
+        <v>108.6</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>110.04</v>
+        <v>108.6</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.99</v>
+        <v>108.85</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.99</v>
+        <v>108.85</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.99</v>
+        <v>108.85</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.99</v>
+        <v>108.85</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>111.68</v>
+        <v>108.99</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>111.68</v>
+        <v>108.99</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>111.68</v>
+        <v>108.99</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>111.68</v>
+        <v>108.99</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>110.57</v>
+        <v>111.68</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>110.57</v>
+        <v>111.68</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>110.57</v>
+        <v>111.68</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>110.57</v>
+        <v>111.68</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>110.19</v>
+        <v>110.57</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>110.19</v>
+        <v>110.57</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>110.19</v>
+        <v>110.57</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>110.19</v>
+        <v>110.57</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>111.86</v>
+        <v>110.19</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>111.86</v>
+        <v>110.19</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>111.86</v>
+        <v>110.19</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>111.86</v>
+        <v>110.19</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>111.23</v>
+        <v>111.86</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>111.23</v>
+        <v>111.86</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>111.23</v>
+        <v>111.86</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>111.23</v>
+        <v>111.86</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>111.47</v>
+        <v>111.23</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>111.47</v>
+        <v>111.23</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>111.47</v>
+        <v>111.23</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>111.47</v>
+        <v>111.23</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>109.8</v>
+        <v>111.47</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>109.8</v>
+        <v>111.47</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>109.8</v>
+        <v>111.47</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>109.8</v>
+        <v>111.47</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>109.11</v>
+        <v>109.8</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>109.11</v>
+        <v>109.8</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>109.11</v>
+        <v>109.8</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>109.11</v>
+        <v>109.8</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>109.61</v>
+        <v>109.11</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>109.61</v>
+        <v>109.11</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>109.61</v>
+        <v>109.11</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>109.61</v>
+        <v>109.11</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>107.77</v>
+        <v>109.61</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>107.77</v>
+        <v>109.61</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>107.77</v>
+        <v>109.61</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>107.77</v>
+        <v>109.61</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>107.98</v>
+        <v>107.77</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>107.98</v>
+        <v>107.77</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>107.98</v>
+        <v>107.77</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>107.98</v>
+        <v>107.77</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>94.73999999999999</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>94.73999999999999</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>94.73999999999999</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>94.73999999999999</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.98</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.98</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.98</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.98</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>95.44</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>95.44</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>95.44</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>95.44</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>97.98999999999999</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>95.94</v>
+        <v>94.94015502929688</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>95.94</v>
+        <v>94.94015502929688</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>95.94</v>
+        <v>94.94015502929688</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>95.94</v>
+        <v>94.94015502929688</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>96.16</v>
+        <v>95.66835021972656</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>96.16</v>
+        <v>95.66835021972656</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>96.16</v>
+        <v>95.66835021972656</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>96.16</v>
+        <v>95.66835021972656</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>97.5</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>97.5</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>97.5</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>97.5</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>94.063232421875</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>94.063232421875</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>94.063232421875</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>96.84999999999999</v>
+        <v>94.063232421875</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>96.45999999999999</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>91.939453125</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>91.939453125</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>91.939453125</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>96.15000000000001</v>
+        <v>91.939453125</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>92.48873901367188</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>92.48873901367188</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>92.48873901367188</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>94.90000000000001</v>
+        <v>92.48873901367188</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>95.77</v>
+        <v>91.03049468994141</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>95.77</v>
+        <v>91.03049468994141</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>95.77</v>
+        <v>91.03049468994141</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>95.77</v>
+        <v>91.03049468994141</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>92.17306518554688</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>92.17306518554688</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>92.17306518554688</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>94.56999999999999</v>
+        <v>92.17306518554688</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>82.48</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>82.48</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>82.48</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>82.48</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>82.56999999999999</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.02893829345703</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.02893829345703</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.02893829345703</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>83.18000000000001</v>
+        <v>82.02893829345703</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>81.86090850830078</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>81.86090850830078</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>81.86090850830078</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>82.98999999999999</v>
+        <v>81.86090850830078</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>81.62033843994141</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>81.62033843994141</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>81.62033843994141</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>82.81999999999999</v>
+        <v>81.62033843994141</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>83.08</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>83.08</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>83.08</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>83.08</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>82.98</v>
+        <v>80.99343109130859</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>82.98</v>
+        <v>80.99343109130859</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>82.98</v>
+        <v>80.99343109130859</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>82.98</v>
+        <v>80.99343109130859</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>82.95999999999999</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>82.98</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>82.98</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>82.98</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>82.98</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>82.52</v>
+        <v>80.12432098388672</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>82.52</v>
+        <v>80.12432098388672</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>82.52</v>
+        <v>80.12432098388672</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>82.52</v>
+        <v>80.12432098388672</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>82.86</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>82.86</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>82.86</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>82.86</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>79.86159515380859</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>79.86159515380859</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>79.86159515380859</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>82.65000000000001</v>
+        <v>79.86159515380859</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>674.15</v>
+        <v>667.739990234375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>674.15</v>
+        <v>667.739990234375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>674.15</v>
+        <v>667.739990234375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>674.15</v>
+        <v>667.739990234375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>667.74</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>667.74</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>667.74</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>667.74</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>577.1799999999999</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>607.29</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>607.29</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>607.29</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>607.29</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>621.87</v>
+        <v>613.536376953125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>621.87</v>
+        <v>613.536376953125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>621.87</v>
+        <v>613.536376953125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>621.87</v>
+        <v>613.536376953125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>617.67431640625</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>617.67431640625</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>617.67431640625</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>614.3099999999999</v>
+        <v>617.67431640625</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>619.25</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>619.25</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>619.25</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>619.25</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>629.0700000000001</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>600.37</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>600.37</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>600.37</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>600.37</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>570.4</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>570.4</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>570.4</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>570.4</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>565.01</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>565.01</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>565.01</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>565.01</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>551.64</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>551.64</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>551.64</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>551.64</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>519.11</v>
+        <v>473.1795959472656</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>519.11</v>
+        <v>473.1795959472656</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>519.11</v>
+        <v>473.1795959472656</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>519.11</v>
+        <v>473.1795959472656</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>662.52</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>662.52</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>662.52</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>662.52</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>660.58</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>660.58</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>660.58</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>660.58</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>597.55</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>597.55</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>597.55</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>597.55</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>631.04</v>
+        <v>634.218017578125</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>631.04</v>
+        <v>634.218017578125</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>631.04</v>
+        <v>634.218017578125</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>631.04</v>
+        <v>634.218017578125</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>636.22</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>636.22</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>636.22</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>636.22</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>627.13</v>
+        <v>624.664794921875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>627.13</v>
+        <v>624.664794921875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>627.13</v>
+        <v>624.664794921875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>627.13</v>
+        <v>624.664794921875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>628.41</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>628.41</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>628.41</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>628.41</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>627.04</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>627.04</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>627.04</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>627.04</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>612.38</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>612.38</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>612.38</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>612.38</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>593.08</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>593.08</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>593.08</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>593.08</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>581.02</v>
+        <v>563.034423828125</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>581.02</v>
+        <v>563.034423828125</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>581.02</v>
+        <v>563.034423828125</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>581.02</v>
+        <v>563.034423828125</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>568.03</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>568.03</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>568.03</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>568.03</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>541.76</v>
+        <v>503.7019348144531</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>541.76</v>
+        <v>503.7019348144531</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>541.76</v>
+        <v>503.7019348144531</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>541.76</v>
+        <v>503.7019348144531</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.97</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.97</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.97</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.97</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>83.06</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>83.06</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>83.06</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>83.06</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>77.11</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>77.11</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>77.11</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>77.11</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>83.81</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>83.81</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>83.81</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>83.81</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>79.66</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>79.66</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>79.66</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>79.66</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>75.44</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>75.44</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>75.44</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>75.44</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>74.94</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>74.94</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>74.94</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>74.94</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>74.63</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>74.63</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>74.63</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>74.63</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>73.45999999999999</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.37</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.37</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.37</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.37</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>68.47</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>68.47</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>68.47</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>68.47</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>69.09</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>69.09</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>69.09</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>69.09</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>66.94</v>
+        <v>61.89026641845703</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>66.94</v>
+        <v>61.89026641845703</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>66.94</v>
+        <v>61.89026641845703</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>66.94</v>
+        <v>61.89026641845703</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>73.36</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>73.36</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>73.36</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>73.36</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.5</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.5</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.5</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.5</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>73.64</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>73.64</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>73.64</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>73.64</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>75.17</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>75.17</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>75.17</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>75.17</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>74.23</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>74.23</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>74.23</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>74.23</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>74.06999999999999</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>74.78</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>74.78</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>74.78</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>74.78</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>74.58</v>
+        <v>72.45805358886719</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>74.58</v>
+        <v>72.45805358886719</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>74.58</v>
+        <v>72.45805358886719</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>74.58</v>
+        <v>72.45805358886719</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>74.37</v>
+        <v>71.66594696044922</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>74.37</v>
+        <v>71.66594696044922</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>74.37</v>
+        <v>71.66594696044922</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>74.37</v>
+        <v>71.66594696044922</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>73.8</v>
+        <v>70.84828186035156</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>73.8</v>
+        <v>70.84828186035156</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>73.8</v>
+        <v>70.84828186035156</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>73.8</v>
+        <v>70.84828186035156</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>73.2</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>73.2</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>73.2</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>73.2</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>73.63</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>73.63</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>73.63</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>73.63</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>72.77</v>
+        <v>70.45079803466797</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>72.77</v>
+        <v>70.45079803466797</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>72.77</v>
+        <v>70.45079803466797</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>72.77</v>
+        <v>70.45079803466797</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.40000000000001</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.64</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.64</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.64</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.64</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>91.64</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>91.64</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>91.64</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>91.64</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>91.62</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>91.62</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>91.62</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>91.62</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>91.65000000000001</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>91.38</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>91.38</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>91.38</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>91.38</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>91.72</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>91.72</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>91.72</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>91.72</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>89.46244049072266</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>89.46244049072266</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>89.46244049072266</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>91.76000000000001</v>
+        <v>89.46244049072266</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>91.75</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>91.75</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>91.75</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>91.75</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>91.77</v>
+        <v>88.83856201171875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>91.77</v>
+        <v>88.83856201171875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>91.77</v>
+        <v>88.83856201171875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>91.77</v>
+        <v>88.83856201171875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>91.75</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>91.75</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>91.75</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>91.75</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>91.73</v>
+        <v>88.22761535644531</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>91.73</v>
+        <v>88.22761535644531</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>91.73</v>
+        <v>88.22761535644531</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>91.73</v>
+        <v>88.22761535644531</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>87.9083251953125</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>87.9083251953125</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>87.9083251953125</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.73999999999999</v>
+        <v>87.9083251953125</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>157.72</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>157.72</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>157.72</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>157.72</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>158.09</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>158.09</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>158.09</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>158.09</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>145.79</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>145.79</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>145.79</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>145.79</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>160.05</v>
+        <v>152.5</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>160.05</v>
+        <v>152.5</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>160.05</v>
+        <v>152.5</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>160.05</v>
+        <v>152.5</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>152.5</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>152.5</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>152.5</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>152.5</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>143.33</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>143.33</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>143.33</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>143.33</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>143.76</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>143.76</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>143.76</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>143.76</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>142.36</v>
+        <v>139.23046875</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>142.36</v>
+        <v>139.23046875</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>142.36</v>
+        <v>139.23046875</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>142.36</v>
+        <v>139.23046875</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>142.55</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>142.55</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>142.55</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>142.55</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>140.27</v>
+        <v>129.8754272460938</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>140.27</v>
+        <v>129.8754272460938</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>140.27</v>
+        <v>129.8754272460938</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>140.27</v>
+        <v>129.8754272460938</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>133.68</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>133.68</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>133.68</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>133.68</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>134.39</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>134.39</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>134.39</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>134.39</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>127.69</v>
+        <v>116.328010559082</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>127.69</v>
+        <v>116.328010559082</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>127.69</v>
+        <v>116.328010559082</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>127.69</v>
+        <v>116.328010559082</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>85.61</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>85.61</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>85.61</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>85.61</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>85.62</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>85.62</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>85.62</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>85.62</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>86.69</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>86.69</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>86.69</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>86.69</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>85.84902954101562</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>85.84902954101562</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>85.84902954101562</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.81999999999999</v>
+        <v>85.84902954101562</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>87.13</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>87.13</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>87.13</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>87.13</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>87.16</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>87.16</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>87.16</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>87.16</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>90.20999999999999</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>86.78591918945312</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>86.78591918945312</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>86.78591918945312</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>90.29000000000001</v>
+        <v>86.78591918945312</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.37</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.37</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.37</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.37</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>83.766845703125</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>83.766845703125</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>83.766845703125</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>86.59999999999999</v>
+        <v>83.766845703125</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>86.92</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>86.92</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>86.92</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>86.92</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.25</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.25</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.25</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.25</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>86.28</v>
+        <v>85.27150726318359</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>86.28</v>
+        <v>85.27150726318359</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>86.28</v>
+        <v>85.27150726318359</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>86.28</v>
+        <v>85.27150726318359</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>58.99</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>58.99</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>58.99</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>58.99</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>58.93</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>58.93</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>58.93</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>58.93</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>54.05</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>54.05</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>54.05</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>54.05</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>58.1</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>58.1</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>58.1</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>58.1</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>56.47</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>56.47</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>56.47</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>56.47</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>53.76</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>53.76</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>53.76</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>53.76</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>54.3</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>54.3</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>54.3</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>54.3</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>54.97</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>54.97</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>54.97</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>54.97</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>54.18</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>54.18</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>54.18</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>54.18</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>51.53</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>51.53</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>51.53</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>51.53</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>49.8</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>49.8</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>49.8</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>49.8</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>49.46</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>49.46</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>49.46</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>49.46</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>47</v>
+        <v>44.02118682861328</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>47</v>
+        <v>44.02118682861328</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>47</v>
+        <v>44.02118682861328</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>47</v>
+        <v>44.02118682861328</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46113</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>108.6</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>108.6</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>108.6</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>108.6</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46082</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.85</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.85</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.85</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.85</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46054</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>108.99</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>108.99</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>108.99</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>108.99</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>111.68</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>111.68</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>111.68</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>111.68</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>110.57</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>110.57</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>110.57</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>110.57</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>45962</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>110.19</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>110.19</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>110.19</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>110.19</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>111.86</v>
+        <v>108.3313674926758</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>111.86</v>
+        <v>108.3313674926758</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>111.86</v>
+        <v>108.3313674926758</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>111.86</v>
+        <v>108.3313674926758</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45901</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>111.23</v>
+        <v>108.1696929931641</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>111.23</v>
+        <v>108.1696929931641</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>111.23</v>
+        <v>108.1696929931641</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>111.23</v>
+        <v>108.1696929931641</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>111.47</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>111.47</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>111.47</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>111.47</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>109.8</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>109.8</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>109.8</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>109.8</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>109.11</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>109.11</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>109.11</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>109.11</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>109.61</v>
+        <v>103.0288238525391</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>109.61</v>
+        <v>103.0288238525391</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>109.61</v>
+        <v>103.0288238525391</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>109.61</v>
+        <v>103.0288238525391</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>107.77</v>
+        <v>102.8165740966797</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>107.77</v>
+        <v>102.8165740966797</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>107.77</v>
+        <v>102.8165740966797</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>107.77</v>
+        <v>102.8165740966797</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.65000152587891</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.66799926757812</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>94.81053161621094</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>97.06257629394531</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>94.94015502929688</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>94.94015502929688</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>94.94015502929688</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>94.94015502929688</v>
+        <v>94.72293853759766</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>95.66835021972656</v>
+        <v>94.94014739990234</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>95.66835021972656</v>
+        <v>94.94014739990234</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>95.66835021972656</v>
+        <v>94.94014739990234</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>95.66835021972656</v>
+        <v>94.94014739990234</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>95.66835784912109</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>95.66835784912109</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>95.66835784912109</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>95.66835784912109</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.73227691650391</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>94.063232421875</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>94.063232421875</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>94.063232421875</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>94.063232421875</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>91.939453125</v>
+        <v>93.45474243164062</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>91.939453125</v>
+        <v>93.45474243164062</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>91.939453125</v>
+        <v>93.45474243164062</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>91.939453125</v>
+        <v>93.45474243164062</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>92.48873901367188</v>
+        <v>91.93944549560547</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>92.48873901367188</v>
+        <v>91.93944549560547</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>92.48873901367188</v>
+        <v>91.93944549560547</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>92.48873901367188</v>
+        <v>91.93944549560547</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>91.03049468994141</v>
+        <v>92.48875427246094</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>91.03049468994141</v>
+        <v>92.48875427246094</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>91.03049468994141</v>
+        <v>92.48875427246094</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>91.03049468994141</v>
+        <v>92.48875427246094</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>92.17306518554688</v>
+        <v>91.03050231933594</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>92.17306518554688</v>
+        <v>91.03050231933594</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>92.17306518554688</v>
+        <v>91.03050231933594</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>92.17306518554688</v>
+        <v>91.03050231933594</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>82.23699951171875</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.08045959472656</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.02893829345703</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.02893829345703</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.02893829345703</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.02893829345703</v>
+        <v>82.46517181396484</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.86090850830078</v>
+        <v>82.02894592285156</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.86090850830078</v>
+        <v>82.02894592285156</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.86090850830078</v>
+        <v>82.02894592285156</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.86090850830078</v>
+        <v>82.02894592285156</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.62033843994141</v>
+        <v>81.86091613769531</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.62033843994141</v>
+        <v>81.86091613769531</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.62033843994141</v>
+        <v>81.86091613769531</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.62033843994141</v>
+        <v>81.86091613769531</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.62034606933594</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.62034606933594</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.62034606933594</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.62034606933594</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>80.99343109130859</v>
+        <v>81.26373291015625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>80.99343109130859</v>
+        <v>81.26373291015625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>80.99343109130859</v>
+        <v>81.26373291015625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>80.99343109130859</v>
+        <v>81.26373291015625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.99343872070312</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.99343872070312</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.99343872070312</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.99343872070312</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>80.76108551025391</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>80.76108551025391</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>80.76108551025391</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>80.76108551025391</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.12432098388672</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.12432098388672</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.12432098388672</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.12432098388672</v>
+        <v>80.05059051513672</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>80.12430572509766</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>80.12430572509766</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>80.12430572509766</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>80.12430572509766</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.86159515380859</v>
+        <v>79.65822601318359</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.86159515380859</v>
+        <v>79.65822601318359</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.86159515380859</v>
+        <v>79.65822601318359</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.86159515380859</v>
+        <v>79.65822601318359</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>738.3099975585938</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>738.3099975585938</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>738.3099975585938</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>738.3099975585938</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.739990234375</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.739990234375</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.739990234375</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.739990234375</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>577.1799926757812</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>606.5252075195312</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>621.0868530273438</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>613.536376953125</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>613.536376953125</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>613.536376953125</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>613.536376953125</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>617.6743774414062</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>617.6743774414062</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>617.6743774414062</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>617.6743774414062</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>627.4693603515625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>627.4693603515625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>627.4693603515625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>627.4693603515625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.8424072265625</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>568.2898559570312</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>568.2898559570312</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>568.2898559570312</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>568.2898559570312</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.9197998046875</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>549.5992431640625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>549.5992431640625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>549.5992431640625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>549.5992431640625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>473.1795959472656</v>
+        <v>516.6093139648438</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>473.1795959472656</v>
+        <v>516.6093139648438</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>473.1795959472656</v>
+        <v>516.6093139648438</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>473.1795959472656</v>
+        <v>516.6093139648438</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>695.489990234375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>695.489990234375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>695.489990234375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>695.489990234375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>660.5800170898438</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>597.5499877929688</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>629.0543212890625</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>634.218017578125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>634.218017578125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>634.218017578125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>634.218017578125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>625.1566772460938</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>624.664794921875</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>624.664794921875</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>624.664794921875</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>624.664794921875</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>623.3029174804688</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>608.7303466796875</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>587.8641357421875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>575.9102172851562</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>563.034423828125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>563.034423828125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>563.034423828125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>563.034423828125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>503.7019348144531</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>503.7019348144531</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>503.7019348144531</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>503.7019348144531</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>86.05999755859375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>86.05999755859375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>86.05999755859375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>86.05999755859375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>83.05999755859375</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>77.11000061035156</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.72309112548828</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.57740020751953</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>75.36177825927734</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>73.20796203613281</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>72.06025695800781</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>69.66825103759766</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.83739471435547</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.44260406494141</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>61.89026641845703</v>
+        <v>64.87525939941406</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>61.89026641845703</v>
+        <v>64.87525939941406</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>61.89026641845703</v>
+        <v>64.87525939941406</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>61.89026641845703</v>
+        <v>64.87525939941406</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>73.25800323486328</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>73.14836120605469</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>74.44166564941406</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>73.26816558837891</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.1102294921875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>73.33033752441406</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.45805358886719</v>
+        <v>72.89495086669922</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.45805358886719</v>
+        <v>72.89495086669922</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.45805358886719</v>
+        <v>72.89495086669922</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.45805358886719</v>
+        <v>72.89495086669922</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>71.66594696044922</v>
+        <v>72.45804595947266</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>71.66594696044922</v>
+        <v>72.45804595947266</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>71.66594696044922</v>
+        <v>72.45804595947266</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>71.66594696044922</v>
+        <v>72.45804595947266</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>70.84828186035156</v>
+        <v>71.66595458984375</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>70.84828186035156</v>
+        <v>71.66595458984375</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>70.84828186035156</v>
+        <v>71.66595458984375</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>70.84828186035156</v>
+        <v>71.66595458984375</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>70.84829711914062</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>70.84829711914062</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>70.84829711914062</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>70.84829711914062</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>71.03702545166016</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>70.45079803466797</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>70.45079803466797</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.45079803466797</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>70.45079803466797</v>
+        <v>69.97576141357422</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.66000366210938</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.66000366210938</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.66000366210938</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.66000366210938</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>91.3699951171875</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>91.10677337646484</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.84531402587891</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.60337829589844</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>90.33644866943359</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>90.03466033935547</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.46244049072266</v>
+        <v>89.7764892578125</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.46244049072266</v>
+        <v>89.7764892578125</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.46244049072266</v>
+        <v>89.7764892578125</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.46244049072266</v>
+        <v>89.7764892578125</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.46241760253906</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.46241760253906</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.46241760253906</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.46241760253906</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>88.83856201171875</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>88.83856201171875</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>88.83856201171875</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>88.83856201171875</v>
+        <v>89.16796112060547</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.83856964111328</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.83856964111328</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.83856964111328</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.83856964111328</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.22761535644531</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.22761535644531</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.22761535644531</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.22761535644531</v>
+        <v>88.52291107177734</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>87.9083251953125</v>
+        <v>88.22762298583984</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>87.9083251953125</v>
+        <v>88.22762298583984</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>87.9083251953125</v>
+        <v>88.22762298583984</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>87.9083251953125</v>
+        <v>88.22762298583984</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>161</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>161</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>161</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>161</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>158.0899963378906</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>145.7899932861328</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>152.5</v>
+        <v>160.0500030517578</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>152.5</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>152.5</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>152.5</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>152.5</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>143.3300018310547</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>140.4122772216797</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>139.23046875</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>139.23046875</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>139.23046875</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>139.23046875</v>
+        <v>139.0448913574219</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>139.23046875</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>139.23046875</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>139.23046875</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>139.23046875</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>129.8754272460938</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>129.8754272460938</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>129.8754272460938</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>129.8754272460938</v>
+        <v>136.2778778076172</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.8754119873047</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.8754119873047</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.8754119873047</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.8754119873047</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>130.5652160644531</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>116.328010559082</v>
+        <v>123.3509750366211</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>116.328010559082</v>
+        <v>123.3509750366211</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>116.328010559082</v>
+        <v>123.3509750366211</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>116.328010559082</v>
+        <v>123.3509750366211</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>85.76000213623047</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>85.76000213623047</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>85.76000213623047</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>85.76000213623047</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.30500030517578</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>86.02733612060547</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>85.84902954101562</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>85.84902954101562</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>85.84902954101562</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>85.84902954101562</v>
+        <v>89.82706451416016</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.84903717041016</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.84903717041016</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.84903717041016</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.84903717041016</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>85.87860107421875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>88.22412872314453</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>86.78591918945312</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>86.78591918945312</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>86.78591918945312</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>86.78591918945312</v>
+        <v>87.98451995849609</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>86.78592681884766</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>86.78592681884766</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>86.78592681884766</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>86.78592681884766</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>83.766845703125</v>
+        <v>83.77748870849609</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>83.766845703125</v>
+        <v>83.77748870849609</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>83.766845703125</v>
+        <v>83.77748870849609</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>83.766845703125</v>
+        <v>83.77748870849609</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>83.76686096191406</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>83.76686096191406</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>83.76686096191406</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>83.76686096191406</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>84.73252105712891</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>84.73252105712891</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>84.73252105712891</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>84.73252105712891</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>85.27150726318359</v>
+        <v>82.53377532958984</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>85.27150726318359</v>
+        <v>82.53377532958984</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>85.27150726318359</v>
+        <v>82.53377532958984</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>85.27150726318359</v>
+        <v>82.53377532958984</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.88000106811523</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.88000106811523</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.88000106811523</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.88000106811523</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.93000030517578</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>54.04999923706055</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.47000122070312</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.7599983215332</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.25311660766602</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.91020202636719</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.13543319702148</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.27578353881836</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.58789443969727</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.25616455078125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>44.02118682861328</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>44.02118682861328</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>44.02118682861328</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>44.02118682861328</v>
+        <v>45.72366333007812</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>109.3600006103516</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>109.3600006103516</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>109.3600006103516</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>109.3600006103516</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>108.4249954223633</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>108.1201934814453</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>110.4087829589844</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.9080657958984</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.5337829589844</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>108.3313674926758</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>108.3313674926758</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>108.3313674926758</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>108.3313674926758</v>
+        <v>109.3401336669922</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>108.1696929931641</v>
+        <v>108.3313827514648</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>108.1696929931641</v>
+        <v>108.3313827514648</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>108.1696929931641</v>
+        <v>108.3313827514648</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>108.1696929931641</v>
+        <v>108.3313827514648</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>108.1697006225586</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>108.1697006225586</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>108.1697006225586</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>108.1697006225586</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>106.1765365600586</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>106.1765365600586</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>106.1765365600586</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>106.1765365600586</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.0799331665039</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.0799331665039</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.0799331665039</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.0799331665039</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>103.0288238525391</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>103.0288238525391</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>103.0288238525391</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>103.0288238525391</v>
+        <v>105.1743316650391</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>102.8165740966797</v>
+        <v>103.0287933349609</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>102.8165740966797</v>
+        <v>103.0287933349609</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>102.8165740966797</v>
+        <v>103.0287933349609</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>102.8165740966797</v>
+        <v>103.0287933349609</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -3005,16 +3005,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.06324005126953</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.06324005126953</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.06324005126953</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>94.063232421875</v>
+        <v>94.06324005126953</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -3024,16 +3024,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>93.45474243164062</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>93.45474243164062</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>93.45474243164062</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>93.45474243164062</v>
+        <v>93.45475006103516</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3062,16 +3062,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.48875427246094</v>
+        <v>92.48876190185547</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.48875427246094</v>
+        <v>92.48876190185547</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.48875427246094</v>
+        <v>92.48876190185547</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.48875427246094</v>
+        <v>92.48876190185547</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3081,16 +3081,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.03050231933594</v>
+        <v>91.03048706054688</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.03050231933594</v>
+        <v>91.03048706054688</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.03050231933594</v>
+        <v>91.03048706054688</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.03050231933594</v>
+        <v>91.03048706054688</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3229,16 +3229,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.46516418457031</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.46516418457031</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.46516418457031</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.46517181396484</v>
+        <v>82.46516418457031</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -3286,16 +3286,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.62034606933594</v>
+        <v>81.62035369873047</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.62034606933594</v>
+        <v>81.62035369873047</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.62034606933594</v>
+        <v>81.62035369873047</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.62034606933594</v>
+        <v>81.62035369873047</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3305,16 +3305,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.26373291015625</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.26373291015625</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.26373291015625</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.26373291015625</v>
+        <v>81.26371765136719</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3324,16 +3324,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.99343872070312</v>
+        <v>80.99342346191406</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.99343872070312</v>
+        <v>80.99342346191406</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.99343872070312</v>
+        <v>80.99342346191406</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.99343872070312</v>
+        <v>80.99342346191406</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -3343,16 +3343,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.76108551025391</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.76108551025391</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.76108551025391</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.76108551025391</v>
+        <v>80.76107025146484</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3381,16 +3381,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>80.12430572509766</v>
+        <v>80.12432861328125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>80.12430572509766</v>
+        <v>80.12432861328125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>80.12430572509766</v>
+        <v>80.12432861328125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>80.12430572509766</v>
+        <v>80.12432861328125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3400,16 +3400,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.65822601318359</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.65822601318359</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.65822601318359</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.65822601318359</v>
+        <v>79.65823364257812</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4037,16 +4037,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>535.3426513671875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>535.3426513671875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>535.3426513671875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>535.3426513671875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4242,16 +4242,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>73.51205444335938</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4299,16 +4299,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>69.66824340820312</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>69.66824340820312</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>69.66824340820312</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>69.66825103759766</v>
+        <v>69.66824340820312</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4318,16 +4318,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>66.83738708496094</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>66.83738708496094</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>66.83738708496094</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>66.83739471435547</v>
+        <v>66.83738708496094</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4524,16 +4524,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>73.26815795898438</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>73.26815795898438</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>73.26815795898438</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>73.26816558837891</v>
+        <v>73.26815795898438</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4562,16 +4562,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.33032989501953</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.33032989501953</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.33032989501953</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.33033752441406</v>
+        <v>73.33032989501953</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4581,16 +4581,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.89495086669922</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.89495086669922</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.89495086669922</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.89495086669922</v>
+        <v>72.89494323730469</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4619,16 +4619,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.66595458984375</v>
+        <v>71.66593933105469</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.66595458984375</v>
+        <v>71.66593933105469</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.66595458984375</v>
+        <v>71.66593933105469</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.66595458984375</v>
+        <v>71.66593933105469</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4638,16 +4638,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>70.84829711914062</v>
+        <v>70.84830474853516</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>70.84829711914062</v>
+        <v>70.84830474853516</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>70.84829711914062</v>
+        <v>70.84830474853516</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>70.84829711914062</v>
+        <v>70.84830474853516</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4657,16 +4657,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>71.03700256347656</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>71.03700256347656</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>71.03700256347656</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.03702545166016</v>
+        <v>71.03700256347656</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -4823,16 +4823,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>90.84530639648438</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>90.84530639648438</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>90.84530639648438</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.84531402587891</v>
+        <v>90.84530639648438</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4842,16 +4842,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.60337066650391</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.60337066650391</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.60337066650391</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.60337829589844</v>
+        <v>90.60337066650391</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4899,16 +4899,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.7764892578125</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.7764892578125</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.7764892578125</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.7764892578125</v>
+        <v>89.77649688720703</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4918,16 +4918,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.46241760253906</v>
+        <v>89.46242523193359</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.46241760253906</v>
+        <v>89.46242523193359</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.46241760253906</v>
+        <v>89.46242523193359</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.46241760253906</v>
+        <v>89.46242523193359</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4937,16 +4937,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.16794586181641</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.16794586181641</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.16794586181641</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>89.16796112060547</v>
+        <v>89.16794586181641</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4956,16 +4956,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.83856964111328</v>
+        <v>88.83857727050781</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.83856964111328</v>
+        <v>88.83857727050781</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.83856964111328</v>
+        <v>88.83857727050781</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.83856964111328</v>
+        <v>88.83857727050781</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4975,16 +4975,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.52292633056641</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.52292633056641</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.52292633056641</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.52291107177734</v>
+        <v>88.52292633056641</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5313,16 +5313,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>123.3509750366211</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>123.3509750366211</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>123.3509750366211</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>123.3509750366211</v>
+        <v>123.3509826660156</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5535,16 +5535,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>87.98452758789062</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>87.98452758789062</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>87.98452758789062</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>87.98451995849609</v>
+        <v>87.98452758789062</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -5573,16 +5573,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>83.77748870849609</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>83.77748870849609</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>83.77748870849609</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>83.77748870849609</v>
+        <v>83.77750396728516</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -5592,16 +5592,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>83.76686096191406</v>
+        <v>83.76686859130859</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>83.76686096191406</v>
+        <v>83.76686859130859</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>83.76686096191406</v>
+        <v>83.76686859130859</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>83.76686096191406</v>
+        <v>83.76686859130859</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -5611,16 +5611,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>84.73252105712891</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>84.73252105712891</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>84.73252105712891</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>84.73252105712891</v>
+        <v>84.73251342773438</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5630,16 +5630,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>82.53377532958984</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>82.53377532958984</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>82.53377532958984</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>82.53377532958984</v>
+        <v>82.53379058837891</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6115,16 +6115,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>108.908073425293</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>108.908073425293</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>108.908073425293</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>108.9080657958984</v>
+        <v>108.908073425293</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -6134,16 +6134,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.5337905883789</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.5337905883789</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.5337905883789</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>108.5337829589844</v>
+        <v>108.5337905883789</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -6172,16 +6172,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>108.3313827514648</v>
+        <v>108.3313751220703</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>108.3313827514648</v>
+        <v>108.3313751220703</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>108.3313827514648</v>
+        <v>108.3313751220703</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>108.3313827514648</v>
+        <v>108.3313751220703</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -6191,16 +6191,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>108.1697006225586</v>
+        <v>108.1697082519531</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>108.1697006225586</v>
+        <v>108.1697082519531</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>108.1697006225586</v>
+        <v>108.1697082519531</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>108.1697006225586</v>
+        <v>108.1697082519531</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -6210,16 +6210,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>106.1765365600586</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>106.1765365600586</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>106.1765365600586</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>106.1765365600586</v>
+        <v>106.1765213012695</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -6229,16 +6229,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>105.0799331665039</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>105.0799331665039</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>105.0799331665039</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>105.0799331665039</v>
+        <v>105.0799407958984</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -6248,16 +6248,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.1743240356445</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.1743240356445</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.1743240356445</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>105.1743316650391</v>
+        <v>105.1743240356445</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -6267,16 +6267,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>103.0287933349609</v>
+        <v>103.0288009643555</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>103.0287933349609</v>
+        <v>103.0288009643555</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>103.0287933349609</v>
+        <v>103.0288009643555</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>103.0287933349609</v>
+        <v>103.0288009643555</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2853,16 +2853,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>94.65000152587891</v>
+        <v>94.33300018310547</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>94.65000152587891</v>
+        <v>94.33300018310547</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>94.65000152587891</v>
+        <v>94.33300018310547</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>94.65000152587891</v>
+        <v>94.33300018310547</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -2872,16 +2872,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.35093688964844</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.35093688964844</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.35093688964844</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.66799926757812</v>
+        <v>94.35093688964844</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -2891,16 +2891,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.49299621582031</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.49299621582031</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.49299621582031</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>94.81053161621094</v>
+        <v>94.49299621582031</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -2910,16 +2910,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>96.73749542236328</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>96.73749542236328</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>96.73749542236328</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>97.06257629394531</v>
+        <v>96.73749542236328</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -2929,16 +2929,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>94.40569305419922</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>94.40569305419922</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>94.40569305419922</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>94.72293853759766</v>
+        <v>94.40569305419922</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -2948,16 +2948,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>94.94014739990234</v>
+        <v>94.62216949462891</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>94.94014739990234</v>
+        <v>94.62216949462891</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>94.94014739990234</v>
+        <v>94.62216949462891</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>94.94014739990234</v>
+        <v>94.62216949462891</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -2967,16 +2967,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>95.66835784912109</v>
+        <v>95.34794616699219</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>95.66835784912109</v>
+        <v>95.34794616699219</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>95.66835784912109</v>
+        <v>95.34794616699219</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>95.66835784912109</v>
+        <v>95.34794616699219</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -2986,16 +2986,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>94.41500091552734</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>94.41500091552734</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>94.41500091552734</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>94.73227691650391</v>
+        <v>94.41500091552734</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3005,16 +3005,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>94.06324005126953</v>
+        <v>93.74819946289062</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>94.06324005126953</v>
+        <v>93.74819946289062</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>94.06324005126953</v>
+        <v>93.74819946289062</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>94.06324005126953</v>
+        <v>93.74819946289062</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -3024,16 +3024,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>93.14175415039062</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>93.14175415039062</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>93.14175415039062</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>93.45475006103516</v>
+        <v>93.14175415039062</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3043,16 +3043,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>91.93944549560547</v>
+        <v>91.63151550292969</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>91.93944549560547</v>
+        <v>91.63151550292969</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>91.93944549560547</v>
+        <v>91.63151550292969</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>91.93944549560547</v>
+        <v>91.63151550292969</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3062,16 +3062,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.48876190185547</v>
+        <v>92.17898559570312</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.48876190185547</v>
+        <v>92.17898559570312</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.48876190185547</v>
+        <v>92.17898559570312</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.48876190185547</v>
+        <v>92.17898559570312</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3081,16 +3081,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.03048706054688</v>
+        <v>90.72559356689453</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.03048706054688</v>
+        <v>90.72559356689453</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.03048706054688</v>
+        <v>90.72559356689453</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.03048706054688</v>
+        <v>90.72559356689453</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3172,16 +3172,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.30000305175781</v>
+        <v>82.05699920654297</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.30000305175781</v>
+        <v>82.05699920654297</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.30000305175781</v>
+        <v>82.05699920654297</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.30000305175781</v>
+        <v>82.05699920654297</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -3191,16 +3191,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>81.99418640136719</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>81.99418640136719</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>81.99418640136719</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>82.23699951171875</v>
+        <v>81.99418640136719</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -3210,16 +3210,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>81.83810424804688</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>81.83810424804688</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>81.83810424804688</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>82.08045959472656</v>
+        <v>81.83810424804688</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -3229,16 +3229,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.46516418457031</v>
+        <v>82.2216796875</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.46516418457031</v>
+        <v>82.2216796875</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.46516418457031</v>
+        <v>82.2216796875</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.46516418457031</v>
+        <v>82.2216796875</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -3248,16 +3248,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>82.02894592285156</v>
+        <v>81.78673553466797</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>82.02894592285156</v>
+        <v>81.78673553466797</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>82.02894592285156</v>
+        <v>81.78673553466797</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>82.02894592285156</v>
+        <v>81.78673553466797</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -3267,16 +3267,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.86091613769531</v>
+        <v>81.61920166015625</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.86091613769531</v>
+        <v>81.61920166015625</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.86091613769531</v>
+        <v>81.61920166015625</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.86091613769531</v>
+        <v>81.61920166015625</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -3286,16 +3286,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.62035369873047</v>
+        <v>81.37934875488281</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.62035369873047</v>
+        <v>81.37934875488281</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.62035369873047</v>
+        <v>81.37934875488281</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.62035369873047</v>
+        <v>81.37934875488281</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3305,16 +3305,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.02379608154297</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.02379608154297</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.02379608154297</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.26371765136719</v>
+        <v>81.02379608154297</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3324,16 +3324,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.99342346191406</v>
+        <v>80.7542724609375</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.99342346191406</v>
+        <v>80.7542724609375</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.99342346191406</v>
+        <v>80.7542724609375</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.99342346191406</v>
+        <v>80.7542724609375</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -3343,16 +3343,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.52261352539062</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.52261352539062</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.52261352539062</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.76107025146484</v>
+        <v>80.52261352539062</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3362,16 +3362,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>79.81423950195312</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>79.81423950195312</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>79.81423950195312</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.05059051513672</v>
+        <v>79.81423950195312</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3381,16 +3381,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>80.12432861328125</v>
+        <v>79.88773345947266</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>80.12432861328125</v>
+        <v>79.88773345947266</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>80.12432861328125</v>
+        <v>79.88773345947266</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>80.12432861328125</v>
+        <v>79.88773345947266</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3400,16 +3400,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>79.42303466796875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>79.42303466796875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>79.42303466796875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.65823364257812</v>
+        <v>79.42303466796875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3604,16 +3604,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>617.6743774414062</v>
+        <v>617.67431640625</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>617.6743774414062</v>
+        <v>617.67431640625</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>617.6743774414062</v>
+        <v>617.67431640625</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>617.6743774414062</v>
+        <v>617.67431640625</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3623,16 +3623,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>627.4693603515625</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>627.4693603515625</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>627.4693603515625</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>627.4693603515625</v>
+        <v>627.4694213867188</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3661,16 +3661,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>568.2898559570312</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>568.2898559570312</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>568.2898559570312</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>568.2898559570312</v>
+        <v>568.2899169921875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3699,16 +3699,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>549.5992431640625</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>549.5992431640625</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>549.5992431640625</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>549.5992431640625</v>
+        <v>549.5991821289062</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3718,16 +3718,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>516.6093139648438</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>516.6093139648438</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>516.6093139648438</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>516.6093139648438</v>
+        <v>516.6094360351562</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4037,16 +4037,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>535.3426513671875</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>535.3426513671875</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>535.3426513671875</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>535.3426513671875</v>
+        <v>535.3427124023438</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4242,16 +4242,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.51205444335938</v>
+        <v>73.51206207275391</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4356,16 +4356,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>64.87525939941406</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>64.87525939941406</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>64.87525939941406</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>64.87525939941406</v>
+        <v>64.87526702880859</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4448,16 +4448,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>73.45999908447266</v>
+        <v>73.21299743652344</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>73.45999908447266</v>
+        <v>73.21299743652344</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>73.45999908447266</v>
+        <v>73.21299743652344</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>73.45999908447266</v>
+        <v>73.21299743652344</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -4467,16 +4467,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.01168060302734</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.01168060302734</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.01168060302734</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.25800323486328</v>
+        <v>73.01168060302734</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -4486,16 +4486,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>72.90241241455078</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>72.90241241455078</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>72.90241241455078</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>73.14836120605469</v>
+        <v>72.90241241455078</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -4505,16 +4505,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>74.19137573242188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>74.19137573242188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>74.19137573242188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>74.44166564941406</v>
+        <v>74.19137573242188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4524,16 +4524,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>73.26815795898438</v>
+        <v>73.02180480957031</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>73.26815795898438</v>
+        <v>73.02180480957031</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>73.26815795898438</v>
+        <v>73.02180480957031</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>73.26815795898438</v>
+        <v>73.02180480957031</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4543,16 +4543,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>72.86440277099609</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>72.86440277099609</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>72.86440277099609</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.1102294921875</v>
+        <v>72.86440277099609</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4562,16 +4562,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.33032989501953</v>
+        <v>73.08377075195312</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.33032989501953</v>
+        <v>73.08377075195312</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.33032989501953</v>
+        <v>73.08377075195312</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.33032989501953</v>
+        <v>73.08377075195312</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4581,16 +4581,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>72.64984893798828</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>72.64984893798828</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>72.64984893798828</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.89494323730469</v>
+        <v>72.64984893798828</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4600,16 +4600,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.45804595947266</v>
+        <v>72.21440887451172</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.45804595947266</v>
+        <v>72.21440887451172</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.45804595947266</v>
+        <v>72.21440887451172</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.45804595947266</v>
+        <v>72.21440887451172</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4619,16 +4619,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.66593933105469</v>
+        <v>71.42497253417969</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.66593933105469</v>
+        <v>71.42497253417969</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.66593933105469</v>
+        <v>71.42497253417969</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.66593933105469</v>
+        <v>71.42497253417969</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4638,16 +4638,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>70.84830474853516</v>
+        <v>70.61007690429688</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>70.84830474853516</v>
+        <v>70.61007690429688</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>70.84830474853516</v>
+        <v>70.61007690429688</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>70.84830474853516</v>
+        <v>70.61007690429688</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4657,16 +4657,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.03700256347656</v>
+        <v>70.79817199707031</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.03700256347656</v>
+        <v>70.79817199707031</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.03700256347656</v>
+        <v>70.79817199707031</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.03700256347656</v>
+        <v>70.79817199707031</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -4676,16 +4676,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>69.74048614501953</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>69.74048614501953</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>69.74048614501953</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>69.97576141357422</v>
+        <v>69.74048614501953</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4766,16 +4766,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.66000366210938</v>
+        <v>91.39100646972656</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.66000366210938</v>
+        <v>91.39100646972656</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.66000366210938</v>
+        <v>91.39100646972656</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.66000366210938</v>
+        <v>91.39100646972656</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -4785,16 +4785,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.10184478759766</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.10184478759766</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.10184478759766</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.3699951171875</v>
+        <v>91.10184478759766</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -4804,16 +4804,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>90.83940124511719</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>90.83940124511719</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>90.83940124511719</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>91.10677337646484</v>
+        <v>90.83940124511719</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -4823,16 +4823,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.84530639648438</v>
+        <v>90.57870483398438</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.84530639648438</v>
+        <v>90.57870483398438</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.84530639648438</v>
+        <v>90.57870483398438</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.84530639648438</v>
+        <v>90.57870483398438</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4842,16 +4842,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.60337066650391</v>
+        <v>90.33747100830078</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.60337066650391</v>
+        <v>90.33747100830078</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.60337066650391</v>
+        <v>90.33747100830078</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.60337066650391</v>
+        <v>90.33747100830078</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4861,16 +4861,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.07134246826172</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.07134246826172</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.07134246826172</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.33644866943359</v>
+        <v>90.07134246826172</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4880,16 +4880,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>89.77043151855469</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>89.77043151855469</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>89.77043151855469</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>90.03466033935547</v>
+        <v>89.77043151855469</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4899,16 +4899,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>89.51302337646484</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>89.51302337646484</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>89.51302337646484</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.77649688720703</v>
+        <v>89.51302337646484</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4918,16 +4918,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.46242523193359</v>
+        <v>89.19986724853516</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.46242523193359</v>
+        <v>89.19986724853516</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.46242523193359</v>
+        <v>89.19986724853516</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.46242523193359</v>
+        <v>89.19986724853516</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4937,16 +4937,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>89.16794586181641</v>
+        <v>88.90627288818359</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>89.16794586181641</v>
+        <v>88.90627288818359</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>89.16794586181641</v>
+        <v>88.90627288818359</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>89.16794586181641</v>
+        <v>88.90627288818359</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4956,16 +4956,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.83857727050781</v>
+        <v>88.57785034179688</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.83857727050781</v>
+        <v>88.57785034179688</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.83857727050781</v>
+        <v>88.57785034179688</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.83857727050781</v>
+        <v>88.57785034179688</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4975,16 +4975,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.52292633056641</v>
+        <v>88.26312255859375</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.52292633056641</v>
+        <v>88.26312255859375</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.52292633056641</v>
+        <v>88.26312255859375</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.52292633056641</v>
+        <v>88.26312255859375</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -4994,16 +4994,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>88.22762298583984</v>
+        <v>87.96868133544922</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>88.22762298583984</v>
+        <v>87.96868133544922</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>88.22762298583984</v>
+        <v>87.96868133544922</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>88.22762298583984</v>
+        <v>87.96868133544922</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5402,16 +5402,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>85.76000213623047</v>
+        <v>85.42400360107422</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>85.76000213623047</v>
+        <v>85.42400360107422</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>85.76000213623047</v>
+        <v>85.42400360107422</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>85.76000213623047</v>
+        <v>85.42400360107422</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -5421,16 +5421,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>84.97077941894531</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>84.97077941894531</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>84.97077941894531</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>85.30500030517578</v>
+        <v>84.97077941894531</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -5440,16 +5440,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.69028472900391</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.69028472900391</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.69028472900391</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>86.02733612060547</v>
+        <v>85.69028472900391</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -5459,16 +5459,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>89.47512817382812</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>89.47512817382812</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>89.47512817382812</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>89.82706451416016</v>
+        <v>89.47512817382812</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -5478,16 +5478,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>85.84903717041016</v>
+        <v>85.51268005371094</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>85.84903717041016</v>
+        <v>85.51268005371094</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>85.84903717041016</v>
+        <v>85.51268005371094</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>85.84903717041016</v>
+        <v>85.51268005371094</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -5497,16 +5497,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.54213714599609</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.54213714599609</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.54213714599609</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>85.87860107421875</v>
+        <v>85.54213714599609</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -5516,16 +5516,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>87.87847137451172</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>87.87847137451172</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>87.87847137451172</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>88.22412872314453</v>
+        <v>87.87847137451172</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -5535,16 +5535,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>87.98452758789062</v>
+        <v>87.63979339599609</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>87.98452758789062</v>
+        <v>87.63979339599609</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>87.98452758789062</v>
+        <v>87.63979339599609</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>87.98452758789062</v>
+        <v>87.63979339599609</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -5554,16 +5554,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>86.78592681884766</v>
+        <v>86.44590759277344</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>86.78592681884766</v>
+        <v>86.44590759277344</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>86.78592681884766</v>
+        <v>86.44590759277344</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>86.78592681884766</v>
+        <v>86.44590759277344</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -5573,16 +5573,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>83.44927978515625</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>83.44927978515625</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>83.44927978515625</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>83.77750396728516</v>
+        <v>83.44927978515625</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -5592,16 +5592,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>83.76686859130859</v>
+        <v>83.43866729736328</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>83.76686859130859</v>
+        <v>83.43866729736328</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>83.76686859130859</v>
+        <v>83.43866729736328</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>83.76686859130859</v>
+        <v>83.43866729736328</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -5611,16 +5611,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>84.40053558349609</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>84.40053558349609</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>84.40053558349609</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>84.73251342773438</v>
+        <v>84.40053558349609</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5630,16 +5630,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>82.21041870117188</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>82.21041870117188</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>82.21041870117188</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>82.53379058837891</v>
+        <v>82.21041870117188</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6039,16 +6039,16 @@
         <v>46143</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>109.3600006103516</v>
+        <v>108.9470062255859</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>109.3600006103516</v>
+        <v>108.9470062255859</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>109.3600006103516</v>
+        <v>108.9470062255859</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>109.3600006103516</v>
+        <v>108.9470062255859</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
@@ -6058,16 +6058,16 @@
         <v>46113</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>108.0155334472656</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>108.0155334472656</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>108.0155334472656</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.4249954223633</v>
+        <v>108.0155334472656</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
@@ -6077,16 +6077,16 @@
         <v>46082</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>107.7118759155273</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>107.7118759155273</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>107.7118759155273</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>108.1201934814453</v>
+        <v>107.7118759155273</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -6096,16 +6096,16 @@
         <v>46054</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>109.9918365478516</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>109.9918365478516</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>109.9918365478516</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>110.4087829589844</v>
+        <v>109.9918365478516</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -6115,16 +6115,16 @@
         <v>46023</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>108.908073425293</v>
+        <v>108.4967803955078</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>108.908073425293</v>
+        <v>108.4967803955078</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>108.908073425293</v>
+        <v>108.4967803955078</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>108.908073425293</v>
+        <v>108.4967803955078</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -6134,16 +6134,16 @@
         <v>45992</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>108.5337905883789</v>
+        <v>108.1239166259766</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>108.5337905883789</v>
+        <v>108.1239166259766</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>108.5337905883789</v>
+        <v>108.1239166259766</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>108.5337905883789</v>
+        <v>108.1239166259766</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -6153,16 +6153,16 @@
         <v>45962</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.9272155761719</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.9272155761719</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.9272155761719</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>109.3401336669922</v>
+        <v>108.9272155761719</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -6172,16 +6172,16 @@
         <v>45931</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>108.3313751220703</v>
+        <v>107.9222717285156</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>108.3313751220703</v>
+        <v>107.9222717285156</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>108.3313751220703</v>
+        <v>107.9222717285156</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>108.3313751220703</v>
+        <v>107.9222717285156</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -6191,16 +6191,16 @@
         <v>45901</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>108.1697082519531</v>
+        <v>107.7611999511719</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>108.1697082519531</v>
+        <v>107.7611999511719</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>108.1697082519531</v>
+        <v>107.7611999511719</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>108.1697082519531</v>
+        <v>107.7611999511719</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -6210,16 +6210,16 @@
         <v>45870</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>105.7755508422852</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>105.7755508422852</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>105.7755508422852</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>106.1765213012695</v>
+        <v>105.7755508422852</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -6229,16 +6229,16 @@
         <v>45839</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>104.6831130981445</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>104.6831130981445</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>104.6831130981445</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>105.0799407958984</v>
+        <v>104.6831130981445</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -6248,16 +6248,16 @@
         <v>45809</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>105.1743240356445</v>
+        <v>104.7771377563477</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>105.1743240356445</v>
+        <v>104.7771377563477</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>105.1743240356445</v>
+        <v>104.7771377563477</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>105.1743240356445</v>
+        <v>104.7771377563477</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -6267,16 +6267,16 @@
         <v>45778</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>103.0288009643555</v>
+        <v>102.6397094726562</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>103.0288009643555</v>
+        <v>102.6397094726562</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>103.0288009643555</v>
+        <v>102.6397094726562</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>103.0288009643555</v>
+        <v>102.6397094726562</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>94.33300018310547</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>94.33300018310547</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>94.33300018310547</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>94.33300018310547</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.35093688964844</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.35093688964844</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.35093688964844</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.35093688964844</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>94.49299621582031</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>94.49299621582031</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>94.49299621582031</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>94.49299621582031</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>96.73749542236328</v>
+        <v>94.1822509765625</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>96.73749542236328</v>
+        <v>94.1822509765625</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>96.73749542236328</v>
+        <v>94.1822509765625</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>96.73749542236328</v>
+        <v>94.1822509765625</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>94.40569305419922</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>94.40569305419922</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>94.40569305419922</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>94.40569305419922</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>94.62216949462891</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>94.62216949462891</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>94.62216949462891</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>94.62216949462891</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>95.34794616699219</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>95.34794616699219</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>95.34794616699219</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>95.34794616699219</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>94.41500091552734</v>
+        <v>95.03439331054688</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>94.41500091552734</v>
+        <v>95.03439331054688</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>94.41500091552734</v>
+        <v>95.03439331054688</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>94.41500091552734</v>
+        <v>95.03439331054688</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>93.74819946289062</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>93.74819946289062</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>93.74819946289062</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>93.74819946289062</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>93.14175415039062</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>93.14175415039062</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>93.14175415039062</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>93.14175415039062</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>91.63151550292969</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>91.63151550292969</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>91.63151550292969</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>91.63151550292969</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.17898559570312</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.17898559570312</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.17898559570312</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.17898559570312</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>90.72559356689453</v>
+        <v>91.8758544921875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>90.72559356689453</v>
+        <v>91.8758544921875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>90.72559356689453</v>
+        <v>91.8758544921875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>90.72559356689453</v>
+        <v>91.8758544921875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.05699920654297</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.05699920654297</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.05699920654297</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.05699920654297</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.99418640136719</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>81.99418640136719</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>81.99418640136719</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>81.99418640136719</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>81.83810424804688</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>81.83810424804688</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>81.83810424804688</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>81.83810424804688</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.2216796875</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.2216796875</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.2216796875</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.2216796875</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.78673553466797</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.78673553466797</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.78673553466797</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.78673553466797</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.61920166015625</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.61920166015625</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.61920166015625</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.61920166015625</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.37934875488281</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.37934875488281</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.37934875488281</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.37934875488281</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.02379608154297</v>
+        <v>81.14345550537109</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.02379608154297</v>
+        <v>81.14345550537109</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.02379608154297</v>
+        <v>81.14345550537109</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.02379608154297</v>
+        <v>81.14345550537109</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.7542724609375</v>
+        <v>80.78893280029297</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.7542724609375</v>
+        <v>80.78893280029297</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.7542724609375</v>
+        <v>80.78893280029297</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.7542724609375</v>
+        <v>80.78893280029297</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.52261352539062</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.52261352539062</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.52261352539062</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.52261352539062</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>79.81423950195312</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>79.81423950195312</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>79.81423950195312</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>79.81423950195312</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>79.88773345947266</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>79.88773345947266</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>79.88773345947266</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>79.88773345947266</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.42303466796875</v>
+        <v>79.65619659423828</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.42303466796875</v>
+        <v>79.65619659423828</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.42303466796875</v>
+        <v>79.65619659423828</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.42303466796875</v>
+        <v>79.65619659423828</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>738.3099975585938</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>738.3099975585938</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>738.3099975585938</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>738.3099975585938</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>737.49951171875</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>737.49951171875</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>737.49951171875</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>667.739990234375</v>
+        <v>737.49951171875</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>577.1799926757812</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>576.54638671875</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>576.54638671875</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>576.54638671875</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>606.5252075195312</v>
+        <v>576.54638671875</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>621.0868530273438</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>620.405029296875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>620.405029296875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>620.405029296875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>613.536376953125</v>
+        <v>620.405029296875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>617.67431640625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>616.996337890625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>616.996337890625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>616.996337890625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>627.4694213867188</v>
+        <v>616.996337890625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>598.8424072265625</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>568.2899169921875</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>567.666015625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>567.666015625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>567.666015625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>562.9197998046875</v>
+        <v>567.666015625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>549.5991821289062</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>548.9959716796875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>548.9959716796875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>548.9959716796875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>516.6094360351562</v>
+        <v>548.9959716796875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>695.489990234375</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>695.489990234375</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>695.489990234375</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>695.489990234375</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>660.5800170898438</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>597.5499877929688</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>595.81494140625</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>595.81494140625</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>595.81494140625</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>629.0543212890625</v>
+        <v>595.81494140625</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>634.218017578125</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>632.37646484375</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>632.37646484375</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>632.37646484375</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>625.1566772460938</v>
+        <v>632.37646484375</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>624.664794921875</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>623.3029174804688</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>608.7303466796875</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>587.8641357421875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>586.1572265625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>586.1572265625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>586.1572265625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>575.9102172851562</v>
+        <v>586.1572265625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>563.034423828125</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>561.3995971679688</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>561.3995971679688</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>561.3995971679688</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>535.3427124023438</v>
+        <v>561.3995971679688</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>86.05999755859375</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>86.05999755859375</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>86.05999755859375</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>86.05999755859375</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>83.05999755859375</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>77.11000061035156</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>83.72309112548828</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>79.57740020751953</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.22085571289062</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.22085571289062</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.22085571289062</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>75.36177825927734</v>
+        <v>79.22085571289062</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.51206207275391</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>73.20796203613281</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>72.87994384765625</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>72.87994384765625</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>72.87994384765625</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.06025695800781</v>
+        <v>72.87994384765625</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>69.66824340820312</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>69.66824340820312</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>69.66824340820312</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>69.66824340820312</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>66.83738708496094</v>
+        <v>69.35608673095703</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>66.83738708496094</v>
+        <v>69.35608673095703</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>66.83738708496094</v>
+        <v>69.35608673095703</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>66.83738708496094</v>
+        <v>69.35608673095703</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.53793334960938</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.53793334960938</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.53793334960938</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>67.44260406494141</v>
+        <v>66.53793334960938</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.14041900634766</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.14041900634766</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.14041900634766</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>64.87526702880859</v>
+        <v>67.14041900634766</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>73.21299743652344</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>73.21299743652344</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>73.21299743652344</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>73.21299743652344</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.01168060302734</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.01168060302734</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.01168060302734</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.01168060302734</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72.90241241455078</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>72.90241241455078</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>72.90241241455078</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>72.90241241455078</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>74.19137573242188</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>74.19137573242188</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>74.19137573242188</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>74.19137573242188</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>73.02180480957031</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>73.02180480957031</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>73.02180480957031</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>73.02180480957031</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>72.86440277099609</v>
+        <v>72.77908325195312</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>72.86440277099609</v>
+        <v>72.77908325195312</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>72.86440277099609</v>
+        <v>72.77908325195312</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>72.86440277099609</v>
+        <v>72.77908325195312</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>73.08377075195312</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>73.08377075195312</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>73.08377075195312</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>73.08377075195312</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.64984893798828</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.64984893798828</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.64984893798828</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.64984893798828</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.21440887451172</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.21440887451172</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.21440887451172</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.21440887451172</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.42497253417969</v>
+        <v>71.97439575195312</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.42497253417969</v>
+        <v>71.97439575195312</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.42497253417969</v>
+        <v>71.97439575195312</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.42497253417969</v>
+        <v>71.97439575195312</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>70.61007690429688</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>70.61007690429688</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>70.61007690429688</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>70.61007690429688</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>70.79817199707031</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>70.79817199707031</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>70.79817199707031</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>70.79817199707031</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>69.74048614501953</v>
+        <v>70.56285095214844</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>69.74048614501953</v>
+        <v>70.56285095214844</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>69.74048614501953</v>
+        <v>70.56285095214844</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>69.74048614501953</v>
+        <v>70.56285095214844</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.39100646972656</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.39100646972656</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.39100646972656</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.39100646972656</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.10184478759766</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.10184478759766</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.10184478759766</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.10184478759766</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>90.83940124511719</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>90.83940124511719</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>90.83940124511719</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>90.83940124511719</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.57870483398438</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.57870483398438</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.57870483398438</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.57870483398438</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.33747100830078</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.33747100830078</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.33747100830078</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.33747100830078</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.07134246826172</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.07134246826172</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.07134246826172</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.07134246826172</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>89.77043151855469</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>89.77043151855469</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>89.77043151855469</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>89.77043151855469</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.51302337646484</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.51302337646484</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.51302337646484</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.51302337646484</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.19986724853516</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.19986724853516</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.19986724853516</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.19986724853516</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>88.90627288818359</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>88.90627288818359</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>88.90627288818359</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>88.90627288818359</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.57785034179688</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.57785034179688</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.57785034179688</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.57785034179688</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.26312255859375</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.26312255859375</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.26312255859375</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.26312255859375</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>87.96868133544922</v>
+        <v>88.0050048828125</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>87.96868133544922</v>
+        <v>88.0050048828125</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>87.96868133544922</v>
+        <v>88.0050048828125</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>87.96868133544922</v>
+        <v>88.0050048828125</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>161</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>161</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>161</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>161</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>158.0899963378906</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>145.7899932861328</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>160.0500030517578</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>152.5</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>152.5</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>152.5</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>152.5</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>143.3300018310547</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>140.4122772216797</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>139.0448913574219</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>139.23046875</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>139.23046875</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>139.23046875</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>139.23046875</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>136.2778778076172</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>129.8754119873047</v>
+        <v>135.5361328125</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>129.8754119873047</v>
+        <v>135.5361328125</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>129.8754119873047</v>
+        <v>135.5361328125</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>129.8754119873047</v>
+        <v>135.5361328125</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>130.5652160644531</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>129.8545684814453</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>129.8545684814453</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>129.8545684814453</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>123.3509826660156</v>
+        <v>129.8545684814453</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>85.42400360107422</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>85.42400360107422</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>85.42400360107422</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>85.42400360107422</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>84.97077941894531</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>84.97077941894531</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>84.97077941894531</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>84.97077941894531</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85.69028472900391</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>85.69028472900391</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>85.69028472900391</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>85.69028472900391</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>89.47512817382812</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>89.47512817382812</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>89.47512817382812</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>89.47512817382812</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>85.51268005371094</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>85.51268005371094</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>85.51268005371094</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>85.51268005371094</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>85.54213714599609</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>85.54213714599609</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>85.54213714599609</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>85.54213714599609</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>87.87847137451172</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>87.87847137451172</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>87.87847137451172</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>87.87847137451172</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>87.63979339599609</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>87.63979339599609</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>87.63979339599609</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>87.63979339599609</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>86.44590759277344</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>86.44590759277344</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>86.44590759277344</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>86.44590759277344</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>83.44927978515625</v>
+        <v>86.12779998779297</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>83.44927978515625</v>
+        <v>86.12779998779297</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>83.44927978515625</v>
+        <v>86.12779998779297</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>83.44927978515625</v>
+        <v>86.12779998779297</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>83.43866729736328</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>83.43866729736328</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>83.43866729736328</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>83.43866729736328</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>84.40053558349609</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>84.40053558349609</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>84.40053558349609</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>84.40053558349609</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>82.21041870117188</v>
+        <v>84.08997344970703</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>82.21041870117188</v>
+        <v>84.08997344970703</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>82.21041870117188</v>
+        <v>84.08997344970703</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>82.21041870117188</v>
+        <v>84.08997344970703</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>59.88000106811523</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>59.88000106811523</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>59.88000106811523</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>59.88000106811523</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>58.93000030517578</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>54.04999923706055</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>58.09999847412109</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>56.47000122070312</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>53.7599983215332</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>53.25311660766602</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.18989944458008</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.18989944458008</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.18989944458008</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>53.91020202636719</v>
+        <v>53.18989944458008</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>53.13543319702148</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>50.27578353881836</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>48.58789443969727</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.53021621704102</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.53021621704102</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.53021621704102</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>48.25616455078125</v>
+        <v>48.53021621704102</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.19887924194336</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.19887924194336</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.19887924194336</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>45.72366333007812</v>
+        <v>48.19887924194336</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>108.9470062255859</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>108.9470062255859</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>108.9470062255859</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>108.9470062255859</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.0155334472656</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.0155334472656</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.0155334472656</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.0155334472656</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>107.7118759155273</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>107.7118759155273</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>107.7118759155273</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>107.7118759155273</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>109.9918365478516</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>109.9918365478516</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>109.9918365478516</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>109.9918365478516</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>108.4967803955078</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>108.4967803955078</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>108.4967803955078</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>108.4967803955078</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>108.1239166259766</v>
+        <v>108.1167831420898</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>108.1239166259766</v>
+        <v>108.1167831420898</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>108.1239166259766</v>
+        <v>108.1167831420898</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>108.1239166259766</v>
+        <v>108.1167831420898</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>108.9272155761719</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>108.9272155761719</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>108.9272155761719</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>108.9272155761719</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>107.9222717285156</v>
+        <v>108.5457000732422</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>107.9222717285156</v>
+        <v>108.5457000732422</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>107.9222717285156</v>
+        <v>108.5457000732422</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>107.9222717285156</v>
+        <v>108.5457000732422</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>107.7611999511719</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>107.7611999511719</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>107.7611999511719</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>107.7611999511719</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>105.7755508422852</v>
+        <v>107.3837966918945</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>105.7755508422852</v>
+        <v>107.3837966918945</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>105.7755508422852</v>
+        <v>107.3837966918945</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>105.7755508422852</v>
+        <v>107.3837966918945</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>104.6831130981445</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>104.6831130981445</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>104.6831130981445</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>104.6831130981445</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>104.7771377563477</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>104.7771377563477</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>104.7771377563477</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>104.7771377563477</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>102.6397094726562</v>
+        <v>104.4101715087891</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>102.6397094726562</v>
+        <v>104.4101715087891</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>102.6397094726562</v>
+        <v>104.4101715087891</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>102.6397094726562</v>
+        <v>104.4101715087891</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.94999694824219</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.94999694824219</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.94999694824219</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.94999694824219</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>94.25900268554688</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>94.02278137207031</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>94.1822509765625</v>
+        <v>94.04066467285156</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>94.1822509765625</v>
+        <v>94.04066467285156</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>94.1822509765625</v>
+        <v>94.04066467285156</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>94.1822509765625</v>
+        <v>94.04066467285156</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>94.18224334716797</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>94.18224334716797</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>94.18224334716797</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>94.18224334716797</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>96.41936492919922</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>95.03439331054688</v>
+        <v>94.31100463867188</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>95.03439331054688</v>
+        <v>94.31100463867188</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>95.03439331054688</v>
+        <v>94.31100463867188</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>95.03439331054688</v>
+        <v>94.31100463867188</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>95.03438568115234</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>95.03438568115234</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>95.03438568115234</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>95.03438568115234</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>94.10450744628906</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>94.10450744628906</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>94.10450744628906</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>94.10450744628906</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>93.43990325927734</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>93.43990325927734</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>93.43990325927734</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>93.43990325927734</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.83544921875</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.83544921875</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.83544921875</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.83544921875</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.8758544921875</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.8758544921875</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.8758544921875</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.8758544921875</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>82</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>82</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>82</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>82</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.87200164794922</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.81915283203125</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.75652313232422</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.98334503173828</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.98334503173828</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.98334503173828</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.98334503173828</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.14345550537109</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.14345550537109</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.14345550537109</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.14345550537109</v>
+        <v>81.38262939453125</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>80.78893280029297</v>
+        <v>81.14346313476562</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>80.78893280029297</v>
+        <v>81.14346313476562</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>80.78893280029297</v>
+        <v>81.14346313476562</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>80.78893280029297</v>
+        <v>81.14346313476562</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.78894805908203</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.78894805908203</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.78894805908203</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.78894805908203</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>80.28921508789062</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.65619659423828</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.65619659423828</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.65619659423828</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.65619659423828</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>567.666015625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>567.666015625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>567.666015625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>567.666015625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>548.9959716796875</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>548.9959716796875</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>548.9959716796875</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>548.9959716796875</v>
+        <v>562.3018188476562</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>595.81494140625</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>595.81494140625</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>595.81494140625</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>595.81494140625</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>632.37646484375</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>632.37646484375</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>632.37646484375</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>632.37646484375</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1572265625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1572265625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1572265625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1572265625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>561.3995971679688</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>561.3995971679688</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>561.3995971679688</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>561.3995971679688</v>
+        <v>574.2379760742188</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>79.22085571289062</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>79.22085571289062</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>79.22085571289062</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>79.22085571289062</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.87994384765625</v>
+        <v>73.18267822265625</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.87994384765625</v>
+        <v>73.18267822265625</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.87994384765625</v>
+        <v>73.18267822265625</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.87994384765625</v>
+        <v>73.18267822265625</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>69.35608673095703</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>69.35608673095703</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>69.35608673095703</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>69.35608673095703</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>66.53793334960938</v>
+        <v>69.35609436035156</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>66.53793334960938</v>
+        <v>69.35609436035156</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>66.53793334960938</v>
+        <v>69.35609436035156</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>66.53793334960938</v>
+        <v>69.35609436035156</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>67.14041900634766</v>
+        <v>66.53791809082031</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>67.14041900634766</v>
+        <v>66.53791809082031</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>67.14041900634766</v>
+        <v>66.53791809082031</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>67.14041900634766</v>
+        <v>66.53791809082031</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>72.23000335693359</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>72.23000335693359</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>72.23000335693359</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>72.23000335693359</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>73.16600036621094</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.96965789794922</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.76901245117188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.66009521484375</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>72.77908325195312</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>72.77908325195312</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>72.77908325195312</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>72.77908325195312</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.77909851074219</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.77909851074219</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.77909851074219</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.77909851074219</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.62223052978516</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.62223052978516</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.62223052978516</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.62223052978516</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.84084320068359</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.84084320068359</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.84084320068359</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.84084320068359</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>71.97439575195312</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>71.97439575195312</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>71.97439575195312</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>71.97439575195312</v>
+        <v>72.40837860107422</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.97438812255859</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.97438812255859</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.97438812255859</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.97438812255859</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>70.56285095214844</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>70.56285095214844</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.56285095214844</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>70.56285095214844</v>
+        <v>70.37537384033203</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.68000030517578</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>91.37200164794922</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>91.12373352050781</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.57375335693359</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.57375335693359</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.57375335693359</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.57375335693359</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>90.07328033447266</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>90.07328033447266</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>90.07328033447266</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>90.07328033447266</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.80792236328125</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.80792236328125</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.80792236328125</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.80792236328125</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.50790405273438</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>89.25125122070312</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>89.25125122070312</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>89.25125122070312</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>89.25125122070312</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.64626312255859</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>88.0050048828125</v>
+        <v>88.31879425048828</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>88.0050048828125</v>
+        <v>88.31879425048828</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>88.0050048828125</v>
+        <v>88.31879425048828</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>88.0050048828125</v>
+        <v>88.31879425048828</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361328125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361328125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361328125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361328125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>129.8545684814453</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>129.8545684814453</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>129.8545684814453</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>129.8545684814453</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>82.25</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>82.25</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>82.25</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>82.25</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>86.10199737548828</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>85.10967254638672</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>85.37497711181641</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>85.37497711181641</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>85.37497711181641</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>85.37497711181641</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>89.14588928222656</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>89.14588928222656</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>89.14588928222656</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>89.14588928222656</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>85.22736358642578</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>86.12779998779297</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>86.12779998779297</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>86.12779998779297</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>86.12779998779297</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>86.12782287597656</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>86.12782287597656</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>86.12782287597656</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>86.12782287597656</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>83.14220428466797</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>84.08997344970703</v>
+        <v>83.13163757324219</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>84.08997344970703</v>
+        <v>83.13163757324219</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>84.08997344970703</v>
+        <v>83.13163757324219</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>84.08997344970703</v>
+        <v>83.13163757324219</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>53.18989944458008</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>53.18989944458008</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>53.18989944458008</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>53.18989944458008</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>48.53021621704102</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>48.53021621704102</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>48.53021621704102</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>48.53021621704102</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>48.19887924194336</v>
+        <v>48.53021240234375</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>48.19887924194336</v>
+        <v>48.53021240234375</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>48.19887924194336</v>
+        <v>48.53021240234375</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>48.19887924194336</v>
+        <v>48.53021240234375</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>106.25</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>106.25</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>106.25</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>106.25</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>108.6880035400391</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>108.5654373168945</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.6372299194336</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>107.3346405029297</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>107.3346405029297</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>107.3346405029297</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>107.3346405029297</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>108.1167831420898</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>108.1167831420898</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>108.1167831420898</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>108.1167831420898</v>
+        <v>109.6066055297852</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>108.1167984008789</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>108.1167984008789</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>108.1167984008789</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>108.1167984008789</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>108.5457000732422</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>108.5457000732422</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>108.5457000732422</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>108.5457000732422</v>
+        <v>107.7452239990234</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>108.5457153320312</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>108.5457153320312</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>108.5457153320312</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>108.5457153320312</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>107.3837966918945</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>107.3837966918945</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>107.3837966918945</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>107.3837966918945</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>107.3837814331055</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>107.3837814331055</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>107.3837814331055</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>107.3837814331055</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>105.4050827026367</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>104.4101715087891</v>
+        <v>104.3164672851562</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>104.4101715087891</v>
+        <v>104.3164672851562</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>104.4101715087891</v>
+        <v>104.3164672851562</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>104.4101715087891</v>
+        <v>104.3164672851562</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2910,16 +2910,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>94.04066467285156</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>94.04066467285156</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>94.04066467285156</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>94.04066467285156</v>
+        <v>94.04065704345703</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -2967,16 +2967,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>94.09523773193359</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3024,16 +3024,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>94.10450744628906</v>
+        <v>94.10452270507812</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>94.10450744628906</v>
+        <v>94.10452270507812</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>94.10450744628906</v>
+        <v>94.10452270507812</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>94.10450744628906</v>
+        <v>94.10452270507812</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3062,16 +3062,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.83544921875</v>
+        <v>92.83543395996094</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.83544921875</v>
+        <v>92.83543395996094</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.83544921875</v>
+        <v>92.83543395996094</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.83544921875</v>
+        <v>92.83543395996094</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3081,16 +3081,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>91.33017730712891</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>91.33017730712891</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>91.33017730712891</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>91.33017730712891</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3248,16 +3248,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.60089874267578</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -3267,16 +3267,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.98334503173828</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.98334503173828</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.98334503173828</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.98334503173828</v>
+        <v>81.98335266113281</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -3286,16 +3286,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.54967498779297</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.54967498779297</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.54967498779297</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.54967498779297</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3343,16 +3343,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.78894805908203</v>
+        <v>80.7889404296875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.78894805908203</v>
+        <v>80.7889404296875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.78894805908203</v>
+        <v>80.7889404296875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.78894805908203</v>
+        <v>80.7889404296875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3362,16 +3362,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.52021789550781</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3400,16 +3400,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.58287811279297</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.58287811279297</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.58287811279297</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.58287811279297</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3904,16 +3904,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>627.2277221679688</v>
+        <v>627.227783203125</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -3942,16 +3942,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>623.3414306640625</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>623.3414306640625</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>623.3414306640625</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>623.3413696289062</v>
+        <v>623.3414306640625</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3999,16 +3999,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>606.9627685546875</v>
+        <v>606.9628295898438</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4280,16 +4280,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>73.18267822265625</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>73.18267822265625</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>73.18267822265625</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>73.18267822265625</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4356,16 +4356,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>66.53791809082031</v>
+        <v>66.53792572021484</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>66.53791809082031</v>
+        <v>66.53792572021484</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>66.53791809082031</v>
+        <v>66.53792572021484</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>66.53791809082031</v>
+        <v>66.53792572021484</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4486,16 +4486,16 @@
         <v>46143</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>72.96965026855469</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>72.96965026855469</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>72.96965026855469</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>72.96965789794922</v>
+        <v>72.96965026855469</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
@@ -4505,16 +4505,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.76900482177734</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.76900482177734</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.76900482177734</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>72.76901245117188</v>
+        <v>72.76900482177734</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4524,16 +4524,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.66010284423828</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.66010284423828</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.66010284423828</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>72.66009521484375</v>
+        <v>72.66010284423828</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4543,16 +4543,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>73.94477844238281</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>73.94477844238281</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>73.94477844238281</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>73.94477844238281</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4581,16 +4581,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.62223052978516</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.62223052978516</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.62223052978516</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.62223052978516</v>
+        <v>72.62221527099609</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4600,16 +4600,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.84084320068359</v>
+        <v>72.84085845947266</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.84084320068359</v>
+        <v>72.84085845947266</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.84084320068359</v>
+        <v>72.84085845947266</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.84084320068359</v>
+        <v>72.84085845947266</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4619,16 +4619,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.40837097167969</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.40837097167969</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.40837097167969</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>72.40837860107422</v>
+        <v>72.40837097167969</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4657,16 +4657,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.18757629394531</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.18757629394531</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.18757629394531</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.18757629394531</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -4676,16 +4676,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>70.37538146972656</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>70.37538146972656</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>70.37538146972656</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>70.37537384033203</v>
+        <v>70.37538146972656</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4823,16 +4823,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.83541870117188</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4842,16 +4842,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.57375335693359</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.57375335693359</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.57375335693359</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.57375335693359</v>
+        <v>90.57373809814453</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4861,16 +4861,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.31379699707031</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.31379699707031</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.31379699707031</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.31379699707031</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4937,16 +4937,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>89.25125122070312</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>89.25125122070312</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>89.25125122070312</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>89.25125122070312</v>
+        <v>89.25124359130859</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4956,16 +4956,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.93901824951172</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4994,16 +4994,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>88.31879425048828</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>88.31879425048828</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>88.31879425048828</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>88.31879425048828</v>
+        <v>88.31880187988281</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5256,16 +5256,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -5275,16 +5275,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.47265625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.47265625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.47265625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.47265625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -5294,16 +5294,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5313,16 +5313,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>129.1685333251953</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>129.1685333251953</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>129.1685333251953</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>129.1685333251953</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5459,16 +5459,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.65811920166016</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -5478,16 +5478,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>85.37497711181641</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>85.37497711181641</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>85.37497711181641</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>85.37497711181641</v>
+        <v>85.37496948242188</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -5516,16 +5516,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>85.19801330566406</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -5535,16 +5535,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.22737121582031</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.22737121582031</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.22737121582031</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>85.22736358642578</v>
+        <v>85.22737121582031</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -5554,16 +5554,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>87.55509948730469</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>87.55509948730469</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>87.55509948730469</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>87.55509948730469</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -5573,16 +5573,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>87.31731414794922</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -5592,16 +5592,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>86.12782287597656</v>
+        <v>86.1278076171875</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>86.12782287597656</v>
+        <v>86.1278076171875</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>86.12782287597656</v>
+        <v>86.1278076171875</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>86.12782287597656</v>
+        <v>86.1278076171875</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -5630,16 +5630,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>83.13163757324219</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>83.13163757324219</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>83.13163757324219</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>83.13163757324219</v>
+        <v>83.13164520263672</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6115,16 +6115,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>107.3346405029297</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>107.3346405029297</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>107.3346405029297</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>107.3346405029297</v>
+        <v>107.3346481323242</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -6134,16 +6134,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>109.6065979003906</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>109.6065979003906</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>109.6065979003906</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>109.6066055297852</v>
+        <v>109.6065979003906</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -6172,16 +6172,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>107.745231628418</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>107.745231628418</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>107.745231628418</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>107.7452239990234</v>
+        <v>107.745231628418</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -6191,16 +6191,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>108.5457153320312</v>
+        <v>108.5457077026367</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>108.5457153320312</v>
+        <v>108.5457077026367</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>108.5457153320312</v>
+        <v>108.5457077026367</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>108.5457153320312</v>
+        <v>108.5457077026367</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -6210,16 +6210,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.5443115234375</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.5443115234375</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.5443115234375</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.5443115234375</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -6229,16 +6229,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>107.3837814331055</v>
+        <v>107.3837890625</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>107.3837814331055</v>
+        <v>107.3837890625</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>107.3837814331055</v>
+        <v>107.3837890625</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>107.3837814331055</v>
+        <v>107.3837890625</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -6248,16 +6248,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>105.4051055908203</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>105.4051055908203</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>105.4051055908203</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>105.4050827026367</v>
+        <v>105.4051055908203</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -6267,16 +6267,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>104.3164672851562</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>104.3164672851562</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>104.3164672851562</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>104.3164672851562</v>
+        <v>104.3164749145508</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2967,16 +2967,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>94.09523773193359</v>
+        <v>94.09523010253906</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -2986,16 +2986,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>94.31100463867188</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>94.31100463867188</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>94.31100463867188</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>94.31100463867188</v>
+        <v>94.31099700927734</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -3024,16 +3024,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>94.10452270507812</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>94.10452270507812</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>94.10452270507812</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>94.10452270507812</v>
+        <v>94.10451507568359</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3043,16 +3043,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>93.43990325927734</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>93.43990325927734</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>93.43990325927734</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>93.43990325927734</v>
+        <v>93.43991088867188</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3062,16 +3062,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.83543395996094</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.83543395996094</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.83543395996094</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.83543395996094</v>
+        <v>92.83544158935547</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -3081,16 +3081,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.33017730712891</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.33017730712891</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.33017730712891</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.33017730712891</v>
+        <v>91.33018493652344</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3248,16 +3248,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.60089874267578</v>
+        <v>81.60089111328125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -3286,16 +3286,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.54967498779297</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.54967498779297</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.54967498779297</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.54967498779297</v>
+        <v>81.5496826171875</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3343,16 +3343,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.7889404296875</v>
+        <v>80.78892517089844</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.7889404296875</v>
+        <v>80.78892517089844</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.7889404296875</v>
+        <v>80.78892517089844</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.7889404296875</v>
+        <v>80.78892517089844</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3362,16 +3362,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.52021789550781</v>
+        <v>80.52021026611328</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3400,16 +3400,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.58287811279297</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.58287811279297</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.58287811279297</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.58287811279297</v>
+        <v>79.5828857421875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3585,16 +3585,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>605.859375</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>605.859375</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>605.859375</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>605.859375</v>
+        <v>605.8594360351562</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -3604,16 +3604,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>620.405029296875</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>620.405029296875</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>620.405029296875</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>620.4050903320312</v>
+        <v>620.405029296875</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -3642,16 +3642,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>616.996337890625</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>616.996337890625</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>616.996337890625</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>616.9962768554688</v>
+        <v>616.996337890625</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -3661,16 +3661,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>626.7806396484375</v>
+        <v>626.7805786132812</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -3680,16 +3680,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>598.18505859375</v>
+        <v>598.1849975585938</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -3718,16 +3718,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>562.3018798828125</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>562.3018798828125</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>562.3018798828125</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>562.3018188476562</v>
+        <v>562.3018798828125</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4543,16 +4543,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.94477844238281</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.94477844238281</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.94477844238281</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.94477844238281</v>
+        <v>73.94477081298828</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4581,16 +4581,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.62220764160156</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.62220764160156</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.62220764160156</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.62221527099609</v>
+        <v>72.62220764160156</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4600,16 +4600,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.84085845947266</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.84085845947266</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.84085845947266</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.84085845947266</v>
+        <v>72.84085083007812</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4638,16 +4638,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.97438812255859</v>
+        <v>71.97440338134766</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.97438812255859</v>
+        <v>71.97440338134766</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.97438812255859</v>
+        <v>71.97440338134766</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.97438812255859</v>
+        <v>71.97440338134766</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4657,16 +4657,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.18757629394531</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.18757629394531</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.18757629394531</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.18757629394531</v>
+        <v>71.18758392333984</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -4823,16 +4823,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.83541870117188</v>
+        <v>90.83542633056641</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -4842,16 +4842,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.57374572753906</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.57374572753906</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.57374572753906</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.57373809814453</v>
+        <v>90.57374572753906</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -4861,16 +4861,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.31379699707031</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.31379699707031</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.31379699707031</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.31379699707031</v>
+        <v>90.31380462646484</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -4880,16 +4880,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>90.07328033447266</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>90.07328033447266</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>90.07328033447266</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>90.07328033447266</v>
+        <v>90.07328796386719</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -4899,16 +4899,16 @@
         <v>45992</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.80792236328125</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.80792236328125</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.80792236328125</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.80792236328125</v>
+        <v>89.80791473388672</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
@@ -4918,16 +4918,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.50789642333984</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.50789642333984</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.50789642333984</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.50790405273438</v>
+        <v>89.50789642333984</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -4937,16 +4937,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.25123596191406</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.25123596191406</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.25123596191406</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>89.25124359130859</v>
+        <v>89.25123596191406</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -4956,16 +4956,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.93901824951172</v>
+        <v>88.93901062011719</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -4975,16 +4975,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.64627075195312</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.64627075195312</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.64627075195312</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.64626312255859</v>
+        <v>88.64627075195312</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5256,16 +5256,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>138.2880859375</v>
+        <v>138.2880706787109</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -5275,16 +5275,16 @@
         <v>45901</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>138.47265625</v>
+        <v>138.4726409912109</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
@@ -5294,16 +5294,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>135.5361328125</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>135.5361328125</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>135.5361328125</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>135.5361175537109</v>
+        <v>135.5361328125</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -5313,16 +5313,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>129.1685333251953</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>129.1685333251953</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>129.1685333251953</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>129.1685333251953</v>
+        <v>129.1685180664062</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5459,16 +5459,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>84.65811920166016</v>
+        <v>84.65811157226562</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -5497,16 +5497,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>89.14588928222656</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>89.14588928222656</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>89.14588928222656</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>89.14588928222656</v>
+        <v>89.14588165283203</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -5516,16 +5516,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>85.19801330566406</v>
+        <v>85.19802093505859</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -5554,16 +5554,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>87.55509948730469</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>87.55509948730469</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>87.55509948730469</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>87.55509948730469</v>
+        <v>87.55510711669922</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -5573,16 +5573,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>87.31731414794922</v>
+        <v>87.31730651855469</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -6096,16 +6096,16 @@
         <v>46113</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>107.6372222900391</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>107.6372222900391</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>107.6372222900391</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>107.6372299194336</v>
+        <v>107.6372222900391</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
@@ -6115,16 +6115,16 @@
         <v>46082</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.3346328735352</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.3346328735352</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.3346328735352</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>107.3346481323242</v>
+        <v>107.3346328735352</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
@@ -6134,16 +6134,16 @@
         <v>46054</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>109.6065979003906</v>
+        <v>109.6066131591797</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>109.6065979003906</v>
+        <v>109.6066131591797</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>109.6065979003906</v>
+        <v>109.6066131591797</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>109.6065979003906</v>
+        <v>109.6066131591797</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
@@ -6153,16 +6153,16 @@
         <v>46023</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>108.1167984008789</v>
+        <v>108.1167907714844</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>108.1167984008789</v>
+        <v>108.1167907714844</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>108.1167984008789</v>
+        <v>108.1167907714844</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>108.1167984008789</v>
+        <v>108.1167907714844</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
@@ -6191,16 +6191,16 @@
         <v>45962</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>108.5457077026367</v>
+        <v>108.5457229614258</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>108.5457077026367</v>
+        <v>108.5457229614258</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>108.5457077026367</v>
+        <v>108.5457229614258</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>108.5457077026367</v>
+        <v>108.5457229614258</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
@@ -6210,16 +6210,16 @@
         <v>45931</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>107.5443115234375</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>107.5443115234375</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>107.5443115234375</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>107.5443115234375</v>
+        <v>107.5442962646484</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
@@ -6248,16 +6248,16 @@
         <v>45870</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>105.4051055908203</v>
+        <v>105.4050903320312</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>105.4051055908203</v>
+        <v>105.4050903320312</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>105.4051055908203</v>
+        <v>105.4050903320312</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>105.4051055908203</v>
+        <v>105.4050903320312</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
@@ -6267,16 +6267,16 @@
         <v>45839</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>104.3164901733398</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>104.3164901733398</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>104.3164901733398</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>104.3164749145508</v>
+        <v>104.3164901733398</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>

--- a/usdn.xlsx
+++ b/usdn.xlsx
@@ -2850,247 +2850,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>92.94999694824219</v>
+        <v>92.40799713134766</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>92.94999694824219</v>
+        <v>92.40799713134766</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>92.94999694824219</v>
+        <v>92.40799713134766</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>92.94999694824219</v>
+        <v>92.40799713134766</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.30038452148438</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.30038452148438</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.30038452148438</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>94.25900268554688</v>
+        <v>92.30038452148438</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>93.60023498535156</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>93.60023498535156</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>93.60023498535156</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>94.02278137207031</v>
+        <v>93.60023498535156</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>93.36566925048828</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>93.36566925048828</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>93.36566925048828</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>94.04065704345703</v>
+        <v>93.36566925048828</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>94.18224334716797</v>
+        <v>93.3834228515625</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>94.18224334716797</v>
+        <v>93.3834228515625</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>94.18224334716797</v>
+        <v>93.3834228515625</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>94.18224334716797</v>
+        <v>93.3834228515625</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>93.52400970458984</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>93.52400970458984</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>93.52400970458984</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>96.41936492919922</v>
+        <v>93.52400970458984</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>95.74551391601562</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>95.74551391601562</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>95.74551391601562</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>94.09523010253906</v>
+        <v>95.74551391601562</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>93.4376220703125</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>93.4376220703125</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>93.4376220703125</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>94.31099700927734</v>
+        <v>93.4376220703125</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>95.03438568115234</v>
+        <v>93.65187072753906</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>95.03438568115234</v>
+        <v>93.65187072753906</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>95.03438568115234</v>
+        <v>93.65187072753906</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>95.03438568115234</v>
+        <v>93.65187072753906</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>94.37021636962891</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>94.37021636962891</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>94.37021636962891</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>94.10451507568359</v>
+        <v>94.37021636962891</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>93.44683074951172</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>93.44683074951172</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>93.44683074951172</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>93.43991088867188</v>
+        <v>93.44683074951172</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>92.78685760498047</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>92.78685760498047</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>92.78685760498047</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>92.83544158935547</v>
+        <v>92.78685760498047</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.18663787841797</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.18663787841797</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.18663787841797</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>91.33018493652344</v>
+        <v>92.18663787841797</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3169,247 +3169,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82</v>
+        <v>81.64599609375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82</v>
+        <v>81.64599609375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82</v>
+        <v>81.64599609375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82</v>
+        <v>81.64599609375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>81.50541687011719</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>81.50541687011719</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>81.50541687011719</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>81.87200164794922</v>
+        <v>81.50541687011719</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.37818908691406</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.37818908691406</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.37818908691406</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>81.81915283203125</v>
+        <v>81.37818908691406</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.32566070556641</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.32566070556641</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.32566070556641</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>81.75652313232422</v>
+        <v>81.32566070556641</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.26341247558594</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.26341247558594</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.26341247558594</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>81.60089111328125</v>
+        <v>81.26341247558594</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.10871887207031</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.10871887207031</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.10871887207031</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>81.98335266113281</v>
+        <v>81.10871887207031</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.48887634277344</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.48887634277344</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.48887634277344</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>81.5496826171875</v>
+        <v>81.48887634277344</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.05780792236328</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.05780792236328</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.05780792236328</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>81.38262939453125</v>
+        <v>81.05780792236328</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>81.14346313476562</v>
+        <v>80.89176177978516</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>81.14346313476562</v>
+        <v>80.89176177978516</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>81.14346313476562</v>
+        <v>80.89176177978516</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>81.14346313476562</v>
+        <v>80.89176177978516</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>80.78892517089844</v>
+        <v>80.65404510498047</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>80.78892517089844</v>
+        <v>80.65404510498047</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>80.78892517089844</v>
+        <v>80.65404510498047</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>80.78892517089844</v>
+        <v>80.65404510498047</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.30165100097656</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.30165100097656</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.30165100097656</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>80.52021026611328</v>
+        <v>80.30165100097656</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.03455352783203</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.03455352783203</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.03455352783203</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>80.28921508789062</v>
+        <v>80.03455352783203</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.80495452880859</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.80495452880859</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.80495452880859</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79.5828857421875</v>
+        <v>79.80495452880859</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3487,247 +3487,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.760009765625</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.760009765625</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.760009765625</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>687.989990234375</v>
+        <v>716.760009765625</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>736.4000244140625</v>
+        <v>687.989990234375</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>737.49951171875</v>
+        <v>736.4000244140625</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>667.0069580078125</v>
+        <v>737.49951171875</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>576.54638671875</v>
+        <v>667.0069580078125</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>605.8594360351562</v>
+        <v>576.54638671875</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>620.405029296875</v>
+        <v>605.859375</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>612.8628540039062</v>
+        <v>620.4050903320312</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>616.996337890625</v>
+        <v>612.8628540039062</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>626.7805786132812</v>
+        <v>616.9962768554688</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>598.1849975585938</v>
+        <v>626.7806396484375</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>567.666015625</v>
+        <v>598.18505859375</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>562.3018798828125</v>
+        <v>567.666015625</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>562.3018798828125</v>
+        <v>567.666015625</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>562.3018798828125</v>
+        <v>567.666015625</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>562.3018798828125</v>
+        <v>567.666015625</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -3806,247 +3806,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>704.8900146484375</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>704.8900146484375</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>704.8900146484375</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>686.6500244140625</v>
+        <v>704.8900146484375</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>686.8099975585938</v>
+        <v>686.6500244140625</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>693.4705200195312</v>
+        <v>686.8099975585938</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>658.6619262695312</v>
+        <v>693.4705200195312</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>595.81494140625</v>
+        <v>658.6619262695312</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>627.227783203125</v>
+        <v>595.81494140625</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>627.227783203125</v>
+        <v>595.81494140625</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>627.227783203125</v>
+        <v>595.81494140625</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>627.227783203125</v>
+        <v>595.81494140625</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>632.37646484375</v>
+        <v>627.2277221679688</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>623.3414306640625</v>
+        <v>632.37646484375</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>623.3414306640625</v>
+        <v>632.37646484375</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>623.3414306640625</v>
+        <v>632.37646484375</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>623.3414306640625</v>
+        <v>632.37646484375</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>622.8510131835938</v>
+        <v>623.3413696289062</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>621.4931030273438</v>
+        <v>622.8510131835938</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>606.9628295898438</v>
+        <v>621.4931030273438</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>586.1572265625</v>
+        <v>606.9627685546875</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1571655273438</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1571655273438</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1571655273438</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>574.2379760742188</v>
+        <v>586.1571655273438</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4125,247 +4125,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>84.58999633789062</v>
+        <v>87.31999969482422</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>85.48999786376953</v>
+        <v>84.58999633789062</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>85.67440032958984</v>
+        <v>85.48999786376953</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>82.68784332275391</v>
+        <v>85.67440032958984</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>76.76450347900391</v>
+        <v>82.68784332275391</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>83.34796905517578</v>
+        <v>76.76450347900391</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>79.22084808349609</v>
+        <v>83.34796905517578</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>75.02411651611328</v>
+        <v>79.22084808349609</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>73.18268585205078</v>
+        <v>75.02411651611328</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>72.87995147705078</v>
+        <v>73.18268585205078</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.73738861083984</v>
+        <v>72.87995147705078</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>69.35609436035156</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>69.35609436035156</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>69.35609436035156</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>69.35609436035156</v>
+        <v>71.73738861083984</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>66.53792572021484</v>
+        <v>69.35610198974609</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>66.53792572021484</v>
+        <v>69.35610198974609</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>66.53792572021484</v>
+        <v>69.35610198974609</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>66.53792572021484</v>
+        <v>69.35610198974609</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4445,247 +4445,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>72.23000335693359</v>
+        <v>71.98699951171875</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>72.23000335693359</v>
+        <v>71.98699951171875</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>72.23000335693359</v>
+        <v>71.98699951171875</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>72.23000335693359</v>
+        <v>71.98699951171875</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>71.72592163085938</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>71.72592163085938</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>71.72592163085938</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>73.16600036621094</v>
+        <v>71.72592163085938</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>72.96965026855469</v>
+        <v>72.65538787841797</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>72.96965026855469</v>
+        <v>72.65538787841797</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>72.96965026855469</v>
+        <v>72.65538787841797</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>72.96965026855469</v>
+        <v>72.65538787841797</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>72.76900482177734</v>
+        <v>72.46041107177734</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>72.76900482177734</v>
+        <v>72.46041107177734</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>72.76900482177734</v>
+        <v>72.46041107177734</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>72.76900482177734</v>
+        <v>72.46041107177734</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>72.66010284423828</v>
+        <v>72.26116943359375</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>72.66010284423828</v>
+        <v>72.26116943359375</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>72.66010284423828</v>
+        <v>72.26116943359375</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>72.66010284423828</v>
+        <v>72.26116943359375</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.15300750732422</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.15300750732422</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.15300750732422</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>73.94477081298828</v>
+        <v>72.15300750732422</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>72.77909851074219</v>
+        <v>73.42873382568359</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>72.77909851074219</v>
+        <v>73.42873382568359</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>72.77909851074219</v>
+        <v>73.42873382568359</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>72.77909851074219</v>
+        <v>73.42873382568359</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>72.62220764160156</v>
+        <v>72.27118682861328</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>72.62220764160156</v>
+        <v>72.27118682861328</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>72.62220764160156</v>
+        <v>72.27118682861328</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>72.62220764160156</v>
+        <v>72.27118682861328</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.11540222167969</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.11540222167969</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.11540222167969</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>72.84085083007812</v>
+        <v>72.11540222167969</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>72.40837097167969</v>
+        <v>72.33251190185547</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>72.40837097167969</v>
+        <v>72.33251190185547</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>72.40837097167969</v>
+        <v>72.33251190185547</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>72.40837097167969</v>
+        <v>72.33251190185547</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>71.97440338134766</v>
+        <v>71.90304565429688</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>71.97440338134766</v>
+        <v>71.90304565429688</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>71.97440338134766</v>
+        <v>71.90304565429688</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>71.97440338134766</v>
+        <v>71.90304565429688</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.47209167480469</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.47209167480469</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.47209167480469</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>71.18758392333984</v>
+        <v>71.47209167480469</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>70.37538146972656</v>
+        <v>70.69078063964844</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>70.37538146972656</v>
+        <v>70.69078063964844</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>70.37538146972656</v>
+        <v>70.69078063964844</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>70.37538146972656</v>
+        <v>70.69078063964844</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -4763,247 +4763,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>91.68000030517578</v>
+        <v>91.3800048828125</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>91.68000030517578</v>
+        <v>91.3800048828125</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>91.68000030517578</v>
+        <v>91.3800048828125</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>91.68000030517578</v>
+        <v>91.3800048828125</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.12777709960938</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.12777709960938</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.12777709960938</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>91.37200164794922</v>
+        <v>91.12777709960938</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>90.82164001464844</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>90.82164001464844</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>90.82164001464844</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>91.12373352050781</v>
+        <v>90.82164001464844</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.57485961914062</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.57485961914062</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.57485961914062</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>90.83542633056641</v>
+        <v>90.57485961914062</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>90.57374572753906</v>
+        <v>90.28828430175781</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>90.57374572753906</v>
+        <v>90.28828430175781</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>90.57374572753906</v>
+        <v>90.28828430175781</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>90.57374572753906</v>
+        <v>90.28828430175781</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.02818298339844</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.02818298339844</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.02818298339844</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>90.31380462646484</v>
+        <v>90.02818298339844</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>89.76979827880859</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>89.76979827880859</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>89.76979827880859</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>90.07328796386719</v>
+        <v>89.76979827880859</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>89.53074645996094</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>89.53074645996094</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>89.53074645996094</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>89.80791473388672</v>
+        <v>89.53074645996094</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>89.50789642333984</v>
+        <v>89.26698303222656</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>89.50789642333984</v>
+        <v>89.26698303222656</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>89.50789642333984</v>
+        <v>89.26698303222656</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>89.50789642333984</v>
+        <v>89.26698303222656</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>89.25123596191406</v>
+        <v>88.96875</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>89.25123596191406</v>
+        <v>88.96875</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>89.25123596191406</v>
+        <v>88.96875</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>89.25123596191406</v>
+        <v>88.96875</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.71364593505859</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.71364593505859</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.71364593505859</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>88.93901062011719</v>
+        <v>88.71364593505859</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>88.64627075195312</v>
+        <v>88.40330505371094</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>88.64627075195312</v>
+        <v>88.40330505371094</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>88.64627075195312</v>
+        <v>88.40330505371094</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>88.64627075195312</v>
+        <v>88.40330505371094</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.1123046875</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.1123046875</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.1123046875</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>88.31880187988281</v>
+        <v>88.1123046875</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5082,247 +5082,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>160.1000061035156</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>160.1000061035156</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>160.1000061035156</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>150.5200042724609</v>
+        <v>160.1000061035156</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>154.2899932861328</v>
+        <v>150.5200042724609</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>160.1236877441406</v>
+        <v>154.2899932861328</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>157.2295227050781</v>
+        <v>160.1236877441406</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>144.9964752197266</v>
+        <v>157.2295227050781</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>159.1788635253906</v>
+        <v>144.9964752197266</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>151.6699523925781</v>
+        <v>159.1788635253906</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>142.5498657226562</v>
+        <v>151.6699523925781</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>139.6480255126953</v>
+        <v>142.5498657226562</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>138.2880706787109</v>
+        <v>139.6480255126953</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>138.4726409912109</v>
+        <v>138.2880859375</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.47265625</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.47265625</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.47265625</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>135.5361328125</v>
+        <v>138.47265625</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>129.1685180664062</v>
+        <v>135.5361175537109</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5399,247 +5399,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.20499420166016</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.20499420166016</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.20499420166016</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>82.25</v>
+        <v>82.20499420166016</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>81.60728454589844</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>81.60728454589844</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>81.60728454589844</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>86.10199737548828</v>
+        <v>81.60728454589844</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>85.42919158935547</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>85.42919158935547</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>85.42919158935547</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>85.10967254638672</v>
+        <v>85.42919158935547</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.44461059570312</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.44461059570312</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.44461059570312</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>84.65811157226562</v>
+        <v>84.44461059570312</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>83.99658966064453</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>83.99658966064453</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>83.99658966064453</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>85.37496948242188</v>
+        <v>83.99658966064453</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>84.70783996582031</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>84.70783996582031</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>84.70783996582031</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>89.14588165283203</v>
+        <v>84.70783996582031</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>88.44928741455078</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>88.44928741455078</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>88.44928741455078</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>85.19802093505859</v>
+        <v>88.44928741455078</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>85.22737121582031</v>
+        <v>84.53227996826172</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>85.22737121582031</v>
+        <v>84.53227996826172</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>85.22737121582031</v>
+        <v>84.53227996826172</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>85.22737121582031</v>
+        <v>84.53227996826172</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>84.56138610839844</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>84.56138610839844</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>84.56138610839844</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>87.55510711669922</v>
+        <v>84.56138610839844</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>86.87094116210938</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>86.87094116210938</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>86.87094116210938</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>87.31730651855469</v>
+        <v>86.87094116210938</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>86.1278076171875</v>
+        <v>86.63501739501953</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>86.1278076171875</v>
+        <v>86.63501739501953</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>86.1278076171875</v>
+        <v>86.63501739501953</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>86.1278076171875</v>
+        <v>86.63501739501953</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>85.45480346679688</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>85.45480346679688</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>85.45480346679688</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>83.14220428466797</v>
+        <v>85.45480346679688</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>82.49253082275391</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>82.49253082275391</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>82.49253082275391</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>83.13164520263672</v>
+        <v>82.49253082275391</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -5718,247 +5718,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>58.75</v>
+        <v>60.52000045776367</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>58.75</v>
+        <v>60.52000045776367</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>58.75</v>
+        <v>60.52000045776367</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>58.75</v>
+        <v>60.52000045776367</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>59.68999862670898</v>
+        <v>58.75</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>59.80891799926758</v>
+        <v>59.68999862670898</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>58.86004638671875</v>
+        <v>59.80891799926758</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>53.98583602905273</v>
+        <v>58.86004638671875</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>58.03102874755859</v>
+        <v>53.98583602905273</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>56.4029655456543</v>
+        <v>58.03102874755859</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>53.69618225097656</v>
+        <v>56.4029655456543</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>53.18990325927734</v>
+        <v>53.69618225097656</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>53.84620666503906</v>
+        <v>53.18990325927734</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>53.07235717773438</v>
+        <v>53.84620666503906</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>50.21610260009766</v>
+        <v>53.07235717773438</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>48.53021240234375</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>48.53021240234375</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>48.53021240234375</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>48.53021240234375</v>
+        <v>50.21610260009766</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
@@ -6036,247 +6036,247 @@
     </row>
     <row r="2" ht="19.2" customHeight="1" s="28">
       <c r="A2" s="36" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>106.25</v>
+        <v>105.765998840332</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>106.25</v>
+        <v>105.765998840332</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>106.25</v>
+        <v>105.765998840332</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>106.25</v>
+        <v>105.765998840332</v>
       </c>
       <c r="F2" s="0" t="inlineStr"/>
       <c r="G2" s="0" t="inlineStr"/>
     </row>
     <row r="3" ht="19.2" customHeight="1" s="28">
       <c r="A3" s="36" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>105.3497467041016</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>105.3497467041016</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>105.3497467041016</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>108.6880035400391</v>
+        <v>105.3497467041016</v>
       </c>
       <c r="F3" s="0" t="inlineStr"/>
       <c r="G3" s="0" t="inlineStr"/>
     </row>
     <row r="4" ht="19.2" customHeight="1" s="28">
       <c r="A4" s="36" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>107.7670974731445</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>107.7670974731445</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>107.7670974731445</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>108.5654373168945</v>
+        <v>107.7670974731445</v>
       </c>
       <c r="F4" s="0" t="inlineStr"/>
       <c r="G4" s="0" t="inlineStr"/>
     </row>
     <row r="5" ht="19.2" customHeight="1" s="28">
       <c r="A5" s="36" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>107.6372222900391</v>
+        <v>107.6455688476562</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>107.6372222900391</v>
+        <v>107.6455688476562</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>107.6372222900391</v>
+        <v>107.6455688476562</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>107.6372222900391</v>
+        <v>107.6455688476562</v>
       </c>
       <c r="F5" s="0" t="inlineStr"/>
       <c r="G5" s="0" t="inlineStr"/>
     </row>
     <row r="6" ht="19.2" customHeight="1" s="28">
       <c r="A6" s="36" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>107.3346328735352</v>
+        <v>106.725227355957</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>107.3346328735352</v>
+        <v>106.725227355957</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>107.3346328735352</v>
+        <v>106.725227355957</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>107.3346328735352</v>
+        <v>106.725227355957</v>
       </c>
       <c r="F6" s="0" t="inlineStr"/>
       <c r="G6" s="0" t="inlineStr"/>
     </row>
     <row r="7" ht="19.2" customHeight="1" s="28">
       <c r="A7" s="36" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>109.6066131591797</v>
+        <v>106.4252090454102</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>109.6066131591797</v>
+        <v>106.4252090454102</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>109.6066131591797</v>
+        <v>106.4252090454102</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>109.6066131591797</v>
+        <v>106.4252090454102</v>
       </c>
       <c r="F7" s="0" t="inlineStr"/>
       <c r="G7" s="0" t="inlineStr"/>
     </row>
     <row r="8" ht="19.2" customHeight="1" s="28">
       <c r="A8" s="36" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>108.1167907714844</v>
+        <v>108.6779098510742</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>108.1167907714844</v>
+        <v>108.6779098510742</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>108.1167907714844</v>
+        <v>108.6779098510742</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>108.1167907714844</v>
+        <v>108.6779098510742</v>
       </c>
       <c r="F8" s="0" t="inlineStr"/>
       <c r="G8" s="0" t="inlineStr"/>
     </row>
     <row r="9" ht="19.2" customHeight="1" s="28">
       <c r="A9" s="36" t="n">
-        <v>45992</v>
+        <v>46023</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>107.745231628418</v>
+        <v>107.2007141113281</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>107.745231628418</v>
+        <v>107.2007141113281</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>107.745231628418</v>
+        <v>107.2007141113281</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>107.745231628418</v>
+        <v>107.2007141113281</v>
       </c>
       <c r="F9" s="0" t="inlineStr"/>
       <c r="G9" s="0" t="inlineStr"/>
     </row>
     <row r="10" ht="19.2" customHeight="1" s="28">
       <c r="A10" s="36" t="n">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>108.5457229614258</v>
+        <v>106.8323135375977</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>108.5457229614258</v>
+        <v>106.8323135375977</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>108.5457229614258</v>
+        <v>106.8323135375977</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>108.5457229614258</v>
+        <v>106.8323135375977</v>
       </c>
       <c r="F10" s="0" t="inlineStr"/>
       <c r="G10" s="0" t="inlineStr"/>
     </row>
     <row r="11" ht="19.2" customHeight="1" s="28">
       <c r="A11" s="36" t="n">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.6260070800781</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.6260070800781</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.6260070800781</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>107.5442962646484</v>
+        <v>107.6260070800781</v>
       </c>
       <c r="F11" s="0" t="inlineStr"/>
       <c r="G11" s="0" t="inlineStr"/>
     </row>
     <row r="12" ht="19.2" customHeight="1" s="28">
       <c r="A12" s="36" t="n">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B12" s="0" t="n">
-        <v>107.3837890625</v>
+        <v>106.6330718994141</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>107.3837890625</v>
+        <v>106.6330718994141</v>
       </c>
       <c r="D12" s="0" t="n">
-        <v>107.3837890625</v>
+        <v>106.6330718994141</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>107.3837890625</v>
+        <v>106.6330718994141</v>
       </c>
       <c r="F12" s="0" t="inlineStr"/>
       <c r="G12" s="0" t="inlineStr"/>
     </row>
     <row r="13" ht="19.2" customHeight="1" s="28">
       <c r="A13" s="36" t="n">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B13" s="0" t="n">
-        <v>105.4050903320312</v>
+        <v>106.4739379882812</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>105.4050903320312</v>
+        <v>106.4739379882812</v>
       </c>
       <c r="D13" s="0" t="n">
-        <v>105.4050903320312</v>
+        <v>106.4739379882812</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>105.4050903320312</v>
+        <v>106.4739379882812</v>
       </c>
       <c r="F13" s="0" t="inlineStr"/>
       <c r="G13" s="0" t="inlineStr"/>
     </row>
     <row r="14" ht="19.2" customHeight="1" s="28">
       <c r="A14" s="37" t="n">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B14" s="0" t="n">
-        <v>104.3164901733398</v>
+        <v>104.5119934082031</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>104.3164901733398</v>
+        <v>104.5119934082031</v>
       </c>
       <c r="D14" s="0" t="n">
-        <v>104.3164901733398</v>
+        <v>104.5119934082031</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>104.3164901733398</v>
+        <v>104.5119934082031</v>
       </c>
       <c r="F14" s="0" t="inlineStr"/>
       <c r="G14" s="0" t="inlineStr"/>
